--- a/outputs/run_manifest.xlsx
+++ b/outputs/run_manifest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://curtin-my.sharepoint.com/personal/21550803_student_curtin_edu_au/Documents/Documents/University/MLaaS/MLaaS-Dataset-Generator/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_6435B315D57BF36E2FFA2211595ED87656CC8980" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9B36C72-C3E3-4229-89BA-ACC00227021F}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_6435B315D57BF36E2FFA2211595ED87656CC8980" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78007087-503D-4620-8461-6AAA465375DC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23955" yWindow="4140" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="runs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="221">
   <si>
     <t>external_run_id</t>
   </si>
@@ -211,21 +211,12 @@
     <t>text</t>
   </si>
   <si>
-    <t>glue</t>
-  </si>
-  <si>
-    <t>distilbert-base-uncased</t>
-  </si>
-  <si>
     <t>train</t>
   </si>
   <si>
     <t>validation</t>
   </si>
   <si>
-    <t>label</t>
-  </si>
-  <si>
     <t>finetune_transfer</t>
   </si>
   <si>
@@ -238,187 +229,28 @@
     <t>registry_curated</t>
   </si>
   <si>
-    <t>https://huggingface.co/distilbert-base-uncased</t>
-  </si>
-  <si>
     <t>inference_only</t>
   </si>
   <si>
     <t>service</t>
   </si>
   <si>
-    <t>roberta-base</t>
-  </si>
-  <si>
     <t>test</t>
   </si>
   <si>
-    <t>https://huggingface.co/roberta-base</t>
-  </si>
-  <si>
-    <t>token_classification</t>
-  </si>
-  <si>
-    <t>conll2003</t>
-  </si>
-  <si>
-    <t>bert-base-cased</t>
-  </si>
-  <si>
-    <t>ner_tags</t>
-  </si>
-  <si>
-    <t>tokens</t>
-  </si>
-  <si>
-    <t>token_sequence</t>
-  </si>
-  <si>
-    <t>token-classification</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/bert-base-cased</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "token_classification", "run_regime": "finetune_transfer", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_tokencls_000006</t>
-  </si>
-  <si>
-    <t>bert-base-cased__conll2003__inference_only__v0</t>
-  </si>
-  <si>
     <t>sgd</t>
   </si>
   <si>
     <t>iid</t>
   </si>
   <si>
-    <t>{"source": "registry", "registry_task": "token_classification", "run_regime": "inference_only", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_tokencls_000007</t>
-  </si>
-  <si>
-    <t>distilbert-base-cased__conll2003__finetune_transfer__v0</t>
-  </si>
-  <si>
     <t>adamw</t>
   </si>
   <si>
-    <t>distilbert-base-cased</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/distilbert-base-cased</t>
-  </si>
-  <si>
-    <t>hf_tokencls_000008</t>
-  </si>
-  <si>
-    <t>distilbert-base-cased__conll2003__inference_only__v0</t>
-  </si>
-  <si>
-    <t>hf_pairscore_000009</t>
-  </si>
-  <si>
-    <t>distilbert-base-uncased__glue_stsb__finetune_transfer__v0</t>
-  </si>
-  <si>
-    <t>sentence_similarity</t>
-  </si>
-  <si>
-    <t>regression</t>
-  </si>
-  <si>
-    <t>stsb</t>
-  </si>
-  <si>
-    <t>['sentence1', 'sentence2']</t>
-  </si>
-  <si>
-    <t>text_pair</t>
-  </si>
-  <si>
-    <t>sentence-similarity</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "sentence_similarity", "run_regime": "finetune_transfer", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_pairscore_000010</t>
-  </si>
-  <si>
-    <t>distilbert-base-uncased__glue_stsb__inference_only__v0</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "sentence_similarity", "run_regime": "inference_only", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_pairscore_000011</t>
-  </si>
-  <si>
-    <t>roberta-base__glue_stsb__finetune_transfer__v0</t>
-  </si>
-  <si>
-    <t>hf_pairscore_000012</t>
-  </si>
-  <si>
-    <t>roberta-base__glue_stsb__inference_only__v0</t>
-  </si>
-  <si>
-    <t>hf_fillmask_000013</t>
-  </si>
-  <si>
-    <t>distilroberta-base__wikitext2__finetune_transfer__v0</t>
-  </si>
-  <si>
-    <t>fill_mask</t>
-  </si>
-  <si>
     <t>wikitext</t>
   </si>
   <si>
     <t>wikitext-2-raw-v1</t>
-  </si>
-  <si>
-    <t>distilroberta-base</t>
-  </si>
-  <si>
-    <t>fill-mask</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/distilroberta-base</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "fill_mask", "run_regime": "finetune_transfer", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_fillmask_000014</t>
-  </si>
-  <si>
-    <t>distilroberta-base__wikitext2__inference_only__v0</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "fill_mask", "run_regime": "inference_only", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_fillmask_000015</t>
-  </si>
-  <si>
-    <t>bert-base-uncased__wikitext2__finetune_transfer__v0</t>
-  </si>
-  <si>
-    <t>bert-base-uncased</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/bert-base-uncased</t>
-  </si>
-  <si>
-    <t>hf_fillmask_000016</t>
-  </si>
-  <si>
-    <t>bert-base-uncased__wikitext2__inference_only__v0</t>
   </si>
   <si>
     <t>hf_textgen_000017</t>
@@ -1217,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BC36"/>
+  <dimension ref="A1:BC25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1389,7 +1221,7 @@
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -1398,7 +1230,7 @@
         <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>57</v>
@@ -1428,25 +1260,25 @@
         <v>8</v>
       </c>
       <c r="N2">
-        <v>0.05</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="O2">
-        <v>0.05</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="P2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="Q2">
         <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="S2">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T2">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="U2">
         <v>2</v>
@@ -1455,19 +1287,19 @@
         <v>1800</v>
       </c>
       <c r="W2">
-        <v>1E-4</v>
+        <v>0.05</v>
       </c>
       <c r="X2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="b">
         <v>1</v>
       </c>
       <c r="AC2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AD2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE2" t="s">
         <v>61</v>
@@ -1476,54 +1308,60 @@
         <v>62</v>
       </c>
       <c r="AG2" t="s">
-        <v>79</v>
+        <v>75</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>76</v>
       </c>
       <c r="AI2" t="s">
         <v>80</v>
       </c>
       <c r="AJ2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP2" t="s">
         <v>65</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AQ2" t="s">
         <v>66</v>
       </c>
-      <c r="AL2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM2" t="s">
+      <c r="AR2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX2" t="s">
         <v>82</v>
       </c>
-      <c r="AP2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR2" t="s">
+      <c r="BB2" t="s">
         <v>83</v>
       </c>
-      <c r="AU2">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX2" t="s">
+      <c r="BC2" t="s">
         <v>84</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>85</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -1532,7 +1370,7 @@
         <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>57</v>
@@ -1559,28 +1397,28 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N3">
-        <v>5.0000000000000002E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="O3">
-        <v>5.0000000000000002E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="P3" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="Q3">
         <v>42</v>
       </c>
       <c r="R3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="S3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T3">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1589,19 +1427,22 @@
         <v>1800</v>
       </c>
       <c r="W3">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="Y3">
+        <v>0.5</v>
       </c>
       <c r="AB3" t="b">
         <v>1</v>
       </c>
       <c r="AC3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE3" t="s">
         <v>61</v>
@@ -1610,54 +1451,60 @@
         <v>62</v>
       </c>
       <c r="AG3" t="s">
-        <v>79</v>
+        <v>75</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>76</v>
       </c>
       <c r="AI3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO3" t="s">
         <v>81</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AP3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU3">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX3" t="s">
         <v>82</v>
       </c>
-      <c r="AP3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR3" t="s">
+      <c r="BB3" t="s">
         <v>83</v>
       </c>
-      <c r="AU3">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>84</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>96</v>
-      </c>
       <c r="BC3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -1666,7 +1513,7 @@
         <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>57</v>
@@ -1693,28 +1540,28 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="O4">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P4" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="Q4">
         <v>42</v>
       </c>
       <c r="R4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="S4">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T4">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="U4">
         <v>2</v>
@@ -1723,22 +1570,19 @@
         <v>1800</v>
       </c>
       <c r="W4">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <v>0.9</v>
       </c>
-      <c r="Y4">
-        <v>0.1</v>
-      </c>
       <c r="AB4" t="b">
         <v>1</v>
       </c>
       <c r="AC4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AD4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE4" t="s">
         <v>61</v>
@@ -1747,54 +1591,60 @@
         <v>62</v>
       </c>
       <c r="AG4" t="s">
-        <v>79</v>
+        <v>75</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>76</v>
       </c>
       <c r="AI4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP4" t="s">
         <v>65</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AQ4" t="s">
         <v>66</v>
       </c>
-      <c r="AL4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM4" t="s">
+      <c r="AR4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU4">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX4" t="s">
         <v>82</v>
       </c>
-      <c r="AP4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU4">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX4" t="s">
+      <c r="BB4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BC4" t="s">
         <v>84</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>96</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -1803,7 +1653,7 @@
         <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>57</v>
@@ -1830,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N5">
         <v>1E-3</v>
@@ -1839,19 +1689,19 @@
         <v>1E-3</v>
       </c>
       <c r="P5" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="Q5">
         <v>42</v>
       </c>
       <c r="R5" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="S5">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T5">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="U5">
         <v>2</v>
@@ -1860,81 +1710,81 @@
         <v>1800</v>
       </c>
       <c r="W5">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="X5">
         <v>0.9</v>
       </c>
-      <c r="Y5">
-        <v>0.1</v>
-      </c>
       <c r="AB5" t="b">
         <v>1</v>
       </c>
       <c r="AC5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD5" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AE5" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="AF5" t="s">
         <v>62</v>
       </c>
       <c r="AG5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>63</v>
       </c>
-      <c r="AH5" t="s">
-        <v>103</v>
-      </c>
-      <c r="AI5" t="s">
+      <c r="AK5" t="s">
         <v>64</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>66</v>
-      </c>
       <c r="AL5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR5" t="s">
         <v>67</v>
       </c>
-      <c r="AM5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AP5" t="s">
+      <c r="AU5">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="s">
         <v>68</v>
       </c>
-      <c r="AQ5" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>105</v>
-      </c>
-      <c r="AU5">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>71</v>
-      </c>
       <c r="AW5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AX5" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="BB5" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="BC5" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -1943,7 +1793,7 @@
         <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>57</v>
@@ -1970,28 +1820,28 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="N6">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="O6">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="P6" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="Q6">
         <v>42</v>
       </c>
       <c r="R6" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="S6">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T6">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="U6">
         <v>2</v>
@@ -2005,76 +1855,79 @@
       <c r="X6">
         <v>0.9</v>
       </c>
-      <c r="Y6">
-        <v>0.3</v>
-      </c>
       <c r="AB6" t="b">
         <v>1</v>
       </c>
       <c r="AC6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AD6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AE6" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="AF6" t="s">
         <v>62</v>
       </c>
       <c r="AG6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>63</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AK6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX6" t="s">
         <v>103</v>
       </c>
-      <c r="AI6" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM6" t="s">
+      <c r="BA6" t="s">
         <v>104</v>
       </c>
-      <c r="AP6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR6" t="s">
+      <c r="BB6" t="s">
         <v>105</v>
       </c>
-      <c r="AU6">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AX6" t="s">
+      <c r="BC6" t="s">
         <v>106</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>72</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -2083,7 +1936,7 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>57</v>
@@ -2110,28 +1963,28 @@
         <v>1</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N7">
-        <v>3.0000000000000001E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="O7">
-        <v>3.0000000000000001E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="P7" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="Q7">
         <v>42</v>
       </c>
       <c r="R7" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="S7">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T7">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -2145,73 +1998,82 @@
       <c r="X7">
         <v>0</v>
       </c>
+      <c r="Y7">
+        <v>0.3</v>
+      </c>
       <c r="AB7" t="b">
         <v>1</v>
       </c>
       <c r="AC7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD7" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AE7" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="AF7" t="s">
         <v>62</v>
       </c>
       <c r="AG7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>63</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AK7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU7">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX7" t="s">
         <v>103</v>
       </c>
-      <c r="AI7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM7" t="s">
+      <c r="BA7" t="s">
         <v>104</v>
       </c>
-      <c r="AP7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR7" t="s">
+      <c r="BB7" t="s">
         <v>105</v>
       </c>
-      <c r="AU7">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>106</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>77</v>
-      </c>
       <c r="BC7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
         <v>55</v>
@@ -2220,7 +2082,7 @@
         <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
         <v>57</v>
@@ -2247,16 +2109,16 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="N8">
-        <v>0.05</v>
+        <v>1E-4</v>
       </c>
       <c r="O8">
-        <v>0.05</v>
+        <v>1E-4</v>
       </c>
       <c r="P8" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="Q8">
         <v>42</v>
@@ -2265,10 +2127,10 @@
         <v>59</v>
       </c>
       <c r="S8">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T8">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="U8">
         <v>2</v>
@@ -2277,81 +2139,84 @@
         <v>1800</v>
       </c>
       <c r="W8">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AB8" t="b">
         <v>1</v>
       </c>
       <c r="AC8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AD8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AE8" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="AF8" t="s">
         <v>62</v>
       </c>
       <c r="AG8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>63</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AK8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX8" t="s">
         <v>103</v>
       </c>
-      <c r="AI8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>104</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>105</v>
-      </c>
-      <c r="AU8">
-        <v>1</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>63</v>
-      </c>
-      <c r="AX8" t="s">
+      <c r="BB8" t="s">
+        <v>113</v>
+      </c>
+      <c r="BC8" t="s">
         <v>106</v>
-      </c>
-      <c r="BB8" t="s">
-        <v>77</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
         <v>55</v>
@@ -2360,7 +2225,7 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
         <v>57</v>
@@ -2387,28 +2252,28 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>1E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="O9">
-        <v>1E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="P9" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="Q9">
         <v>42</v>
       </c>
       <c r="R9" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="S9">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="T9">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="U9">
         <v>2</v>
@@ -2420,16 +2285,19 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0.1</v>
       </c>
       <c r="AB9" t="b">
         <v>1</v>
       </c>
       <c r="AC9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD9" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="AE9" t="s">
         <v>61</v>
@@ -2438,57 +2306,60 @@
         <v>62</v>
       </c>
       <c r="AG9" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="AH9" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="AI9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="AJ9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL9" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="AM9" t="s">
-        <v>62</v>
+        <v>101</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>102</v>
       </c>
       <c r="AP9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU9">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="s">
         <v>68</v>
       </c>
-      <c r="AQ9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU9">
-        <v>1</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>71</v>
-      </c>
       <c r="AW9" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="AX9" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="BB9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="BC9" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
@@ -2497,7 +2368,7 @@
         <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
         <v>57</v>
@@ -2524,28 +2395,25 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N10">
-        <v>1.0000000000000001E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="O10">
-        <v>1.0000000000000001E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="P10" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="Q10">
         <v>42</v>
       </c>
       <c r="R10" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="S10">
-        <v>1200</v>
-      </c>
-      <c r="T10">
-        <v>128</v>
+        <v>800</v>
       </c>
       <c r="U10">
         <v>2</v>
@@ -2554,22 +2422,19 @@
         <v>1800</v>
       </c>
       <c r="W10">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AB10" t="b">
         <v>1</v>
       </c>
       <c r="AC10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AD10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AE10" t="s">
         <v>61</v>
@@ -2578,49 +2443,52 @@
         <v>62</v>
       </c>
       <c r="AG10" t="s">
-        <v>118</v>
-      </c>
-      <c r="AH10" t="s">
         <v>119</v>
       </c>
       <c r="AI10" t="s">
         <v>120</v>
       </c>
       <c r="AJ10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL10" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="AM10" t="s">
         <v>62</v>
       </c>
+      <c r="AN10" t="s">
+        <v>122</v>
+      </c>
       <c r="AP10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="AQ10" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AR10" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="AU10">
         <v>1</v>
       </c>
       <c r="AV10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AW10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AX10" t="s">
-        <v>121</v>
+        <v>124</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>104</v>
       </c>
       <c r="BB10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="BC10" t="s">
         <v>126</v>
@@ -2664,16 +2532,16 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>2.0000000000000002E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="O11">
-        <v>2.0000000000000002E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="P11" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="Q11">
         <v>42</v>
@@ -2682,10 +2550,7 @@
         <v>59</v>
       </c>
       <c r="S11">
-        <v>1200</v>
-      </c>
-      <c r="T11">
-        <v>128</v>
+        <v>800</v>
       </c>
       <c r="U11">
         <v>2</v>
@@ -2694,22 +2559,22 @@
         <v>1800</v>
       </c>
       <c r="W11">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="X11">
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AB11" t="b">
         <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AE11" t="s">
         <v>61</v>
@@ -2718,57 +2583,60 @@
         <v>62</v>
       </c>
       <c r="AG11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AH11" t="s">
         <v>119</v>
       </c>
       <c r="AI11" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL11" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="AM11" t="s">
         <v>62</v>
       </c>
+      <c r="AN11" t="s">
+        <v>122</v>
+      </c>
       <c r="AP11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AU11">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="s">
         <v>68</v>
       </c>
-      <c r="AQ11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU11">
-        <v>1</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>71</v>
-      </c>
       <c r="AW11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AX11" t="s">
-        <v>121</v>
+        <v>124</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>104</v>
       </c>
       <c r="BB11" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="BC11" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
@@ -2777,7 +2645,7 @@
         <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s">
         <v>57</v>
@@ -2804,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="M12">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N12">
         <v>5.0000000000000001E-3</v>
@@ -2813,7 +2681,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="P12" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="Q12">
         <v>42</v>
@@ -2822,10 +2690,7 @@
         <v>59</v>
       </c>
       <c r="S12">
-        <v>1200</v>
-      </c>
-      <c r="T12">
-        <v>128</v>
+        <v>800</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -2846,10 +2711,10 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AD12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AE12" t="s">
         <v>61</v>
@@ -2858,49 +2723,52 @@
         <v>62</v>
       </c>
       <c r="AG12" t="s">
-        <v>118</v>
-      </c>
-      <c r="AH12" t="s">
         <v>119</v>
       </c>
       <c r="AI12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AJ12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL12" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="AM12" t="s">
         <v>62</v>
       </c>
+      <c r="AN12" t="s">
+        <v>122</v>
+      </c>
       <c r="AP12" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="AQ12" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AR12" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="AU12">
         <v>1</v>
       </c>
       <c r="AV12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AW12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AX12" t="s">
-        <v>121</v>
+        <v>124</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>133</v>
       </c>
       <c r="BB12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BC12" t="s">
         <v>126</v>
@@ -2908,7 +2776,7 @@
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s">
         <v>55</v>
@@ -2917,7 +2785,7 @@
         <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E13" t="s">
         <v>57</v>
@@ -2947,25 +2815,22 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>2.0000000000000002E-5</v>
+        <v>0.01</v>
       </c>
       <c r="O13">
-        <v>2.0000000000000002E-5</v>
+        <v>0.01</v>
       </c>
       <c r="P13" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="Q13">
         <v>42</v>
       </c>
       <c r="R13" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="S13">
-        <v>1000</v>
-      </c>
-      <c r="T13">
-        <v>256</v>
+        <v>800</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -2974,19 +2839,22 @@
         <v>1800</v>
       </c>
       <c r="W13">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="Y13">
+        <v>0.1</v>
       </c>
       <c r="AB13" t="b">
         <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD13" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="AE13" t="s">
         <v>61</v>
@@ -2995,60 +2863,60 @@
         <v>62</v>
       </c>
       <c r="AG13" t="s">
-        <v>118</v>
-      </c>
-      <c r="AH13" t="s">
         <v>119</v>
       </c>
       <c r="AI13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AJ13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL13" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="AM13" t="s">
         <v>62</v>
       </c>
-      <c r="AO13" t="s">
-        <v>137</v>
+      <c r="AN13" t="s">
+        <v>122</v>
       </c>
       <c r="AP13" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AU13">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="s">
         <v>68</v>
       </c>
-      <c r="AQ13" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU13">
-        <v>1</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>71</v>
-      </c>
       <c r="AW13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AX13" t="s">
-        <v>138</v>
+        <v>124</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>133</v>
       </c>
       <c r="BB13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="BC13" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B14" t="s">
         <v>55</v>
@@ -3057,7 +2925,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
         <v>57</v>
@@ -3087,25 +2955,22 @@
         <v>16</v>
       </c>
       <c r="N14">
-        <v>1E-4</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="O14">
-        <v>1E-4</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P14" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="Q14">
         <v>42</v>
       </c>
       <c r="R14" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="S14">
-        <v>1000</v>
-      </c>
-      <c r="T14">
-        <v>256</v>
+        <v>1500</v>
       </c>
       <c r="U14">
         <v>2</v>
@@ -3114,84 +2979,81 @@
         <v>1800</v>
       </c>
       <c r="W14">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>0.9</v>
-      </c>
-      <c r="Y14">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="b">
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AD14" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AE14" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="AF14" t="s">
         <v>62</v>
       </c>
       <c r="AG14" t="s">
-        <v>118</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="AI14" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="AJ14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL14" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="AM14" t="s">
         <v>62</v>
       </c>
-      <c r="AO14" t="s">
-        <v>137</v>
+      <c r="AN14" t="s">
+        <v>122</v>
       </c>
       <c r="AP14" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="AQ14" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AR14" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="AU14">
         <v>1</v>
       </c>
       <c r="AV14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AW14" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="AX14" t="s">
-        <v>138</v>
+        <v>145</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>146</v>
       </c>
       <c r="BB14" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="BC14" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s">
         <v>55</v>
@@ -3200,7 +3062,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E15" t="s">
         <v>57</v>
@@ -3230,25 +3092,22 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>5.0000000000000001E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="O15">
-        <v>5.0000000000000001E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="P15" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="Q15">
         <v>42</v>
       </c>
       <c r="R15" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="S15">
-        <v>1000</v>
-      </c>
-      <c r="T15">
-        <v>256</v>
+        <v>1500</v>
       </c>
       <c r="U15">
         <v>2</v>
@@ -3260,78 +3119,78 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="b">
         <v>1</v>
       </c>
       <c r="AC15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AE15" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="s">
         <v>62</v>
       </c>
       <c r="AG15" t="s">
-        <v>118</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="AI15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AJ15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL15" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="AM15" t="s">
         <v>62</v>
       </c>
-      <c r="AO15" t="s">
-        <v>137</v>
+      <c r="AN15" t="s">
+        <v>122</v>
       </c>
       <c r="AP15" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>144</v>
+      </c>
+      <c r="AU15">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="s">
         <v>68</v>
       </c>
-      <c r="AQ15" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU15">
-        <v>1</v>
-      </c>
-      <c r="AV15" t="s">
-        <v>71</v>
-      </c>
       <c r="AW15" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="AX15" t="s">
-        <v>138</v>
+        <v>145</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>146</v>
       </c>
       <c r="BB15" t="s">
         <v>147</v>
       </c>
       <c r="BC15" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s">
         <v>55</v>
@@ -3340,7 +3199,7 @@
         <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E16" t="s">
         <v>57</v>
@@ -3382,13 +3241,10 @@
         <v>42</v>
       </c>
       <c r="R16" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="S16">
-        <v>1000</v>
-      </c>
-      <c r="T16">
-        <v>256</v>
+        <v>1500</v>
       </c>
       <c r="U16">
         <v>2</v>
@@ -3397,81 +3253,84 @@
         <v>1800</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="X16">
         <v>0.9</v>
       </c>
+      <c r="Y16">
+        <v>0.3</v>
+      </c>
       <c r="AB16" t="b">
         <v>1</v>
       </c>
       <c r="AC16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AD16" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AE16" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="AF16" t="s">
         <v>62</v>
       </c>
       <c r="AG16" t="s">
-        <v>118</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="AI16" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AJ16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL16" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="AM16" t="s">
         <v>62</v>
       </c>
-      <c r="AO16" t="s">
-        <v>137</v>
+      <c r="AN16" t="s">
+        <v>122</v>
       </c>
       <c r="AP16" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="AQ16" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AR16" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="AU16">
         <v>1</v>
       </c>
       <c r="AV16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AW16" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="AX16" t="s">
-        <v>138</v>
+        <v>145</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>155</v>
       </c>
       <c r="BB16" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="BC16" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B17" t="s">
         <v>55</v>
@@ -3480,7 +3339,7 @@
         <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
         <v>57</v>
@@ -3507,28 +3366,25 @@
         <v>1</v>
       </c>
       <c r="M17">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>1E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="O17">
-        <v>1E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="P17" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="Q17">
         <v>42</v>
       </c>
       <c r="R17" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="S17">
-        <v>1000</v>
-      </c>
-      <c r="T17">
-        <v>256</v>
+        <v>1500</v>
       </c>
       <c r="U17">
         <v>2</v>
@@ -3540,81 +3396,78 @@
         <v>1E-4</v>
       </c>
       <c r="X17">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="b">
         <v>1</v>
       </c>
       <c r="AC17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD17" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="AE17" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="AF17" t="s">
         <v>62</v>
       </c>
       <c r="AG17" t="s">
-        <v>153</v>
-      </c>
-      <c r="AH17" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI17" t="s">
         <v>154</v>
       </c>
-      <c r="AI17" t="s">
+      <c r="AJ17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>143</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>144</v>
+      </c>
+      <c r="AU17">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>141</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>145</v>
+      </c>
+      <c r="BA17" t="s">
         <v>155</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL17" t="s">
+      <c r="BB17" t="s">
         <v>156</v>
       </c>
-      <c r="AM17" t="s">
-        <v>157</v>
-      </c>
-      <c r="AO17" t="s">
-        <v>158</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ17" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU17">
-        <v>1</v>
-      </c>
-      <c r="AV17" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW17" t="s">
-        <v>153</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>159</v>
-      </c>
-      <c r="BA17" t="s">
-        <v>160</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>161</v>
-      </c>
       <c r="BC17" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s">
         <v>55</v>
@@ -3623,7 +3476,7 @@
         <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E18" t="s">
         <v>57</v>
@@ -3650,28 +3503,25 @@
         <v>1</v>
       </c>
       <c r="M18">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N18">
-        <v>2.0000000000000002E-5</v>
+        <v>5.0000000000000002E-5</v>
       </c>
       <c r="O18">
-        <v>2.0000000000000002E-5</v>
+        <v>5.0000000000000002E-5</v>
       </c>
       <c r="P18" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="Q18">
         <v>42</v>
       </c>
       <c r="R18" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="S18">
-        <v>1000</v>
-      </c>
-      <c r="T18">
-        <v>256</v>
+        <v>1200</v>
       </c>
       <c r="U18">
         <v>2</v>
@@ -3680,87 +3530,81 @@
         <v>1800</v>
       </c>
       <c r="W18">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="X18">
         <v>0</v>
       </c>
-      <c r="Y18">
-        <v>0.3</v>
-      </c>
       <c r="AB18" t="b">
         <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AD18" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="AE18" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="AF18" t="s">
         <v>62</v>
       </c>
       <c r="AG18" t="s">
-        <v>153</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="AI18" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="AJ18" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>165</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP18" t="s">
         <v>65</v>
       </c>
-      <c r="AK18" t="s">
+      <c r="AQ18" t="s">
         <v>66</v>
       </c>
-      <c r="AL18" t="s">
-        <v>156</v>
-      </c>
-      <c r="AM18" t="s">
-        <v>157</v>
-      </c>
-      <c r="AO18" t="s">
-        <v>158</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ18" t="s">
-        <v>74</v>
-      </c>
       <c r="AR18" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="AU18">
         <v>1</v>
       </c>
       <c r="AV18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AW18" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="AX18" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="BA18" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="BB18" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="BC18" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s">
         <v>55</v>
@@ -3769,7 +3613,7 @@
         <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
         <v>57</v>
@@ -3796,16 +3640,16 @@
         <v>1</v>
       </c>
       <c r="M19">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N19">
-        <v>1E-4</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="O19">
-        <v>1E-4</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="P19" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="Q19">
         <v>42</v>
@@ -3814,10 +3658,7 @@
         <v>59</v>
       </c>
       <c r="S19">
-        <v>1000</v>
-      </c>
-      <c r="T19">
-        <v>256</v>
+        <v>1200</v>
       </c>
       <c r="U19">
         <v>2</v>
@@ -3826,84 +3667,84 @@
         <v>1800</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="X19">
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AB19" t="b">
         <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD19" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="AE19" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="AF19" t="s">
         <v>62</v>
       </c>
       <c r="AG19" t="s">
-        <v>153</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="AI19" t="s">
+        <v>164</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>165</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>166</v>
+      </c>
+      <c r="AU19">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>163</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>167</v>
+      </c>
+      <c r="BA19" t="s">
         <v>168</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>156</v>
-      </c>
-      <c r="AM19" t="s">
-        <v>157</v>
-      </c>
-      <c r="AO19" t="s">
-        <v>158</v>
-      </c>
-      <c r="AP19" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU19">
-        <v>1</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW19" t="s">
-        <v>153</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>159</v>
       </c>
       <c r="BB19" t="s">
         <v>169</v>
       </c>
       <c r="BC19" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B20" t="s">
         <v>55</v>
@@ -3912,7 +3753,7 @@
         <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E20" t="s">
         <v>57</v>
@@ -3939,28 +3780,25 @@
         <v>1</v>
       </c>
       <c r="M20">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N20">
-        <v>1.0000000000000001E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="O20">
-        <v>1.0000000000000001E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="P20" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="Q20">
         <v>42</v>
       </c>
       <c r="R20" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="S20">
-        <v>1000</v>
-      </c>
-      <c r="T20">
-        <v>256</v>
+        <v>1200</v>
       </c>
       <c r="U20">
         <v>2</v>
@@ -3969,13 +3807,10 @@
         <v>1800</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="X20">
         <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0.1</v>
       </c>
       <c r="AB20" t="b">
         <v>1</v>
@@ -3984,69 +3819,69 @@
         <v>55</v>
       </c>
       <c r="AD20" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="AE20" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="AF20" t="s">
         <v>62</v>
       </c>
       <c r="AG20" t="s">
-        <v>153</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="AI20" t="s">
+        <v>176</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>165</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>166</v>
+      </c>
+      <c r="AU20">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>163</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>167</v>
+      </c>
+      <c r="BA20" t="s">
         <v>168</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>156</v>
-      </c>
-      <c r="AM20" t="s">
-        <v>157</v>
-      </c>
-      <c r="AO20" t="s">
-        <v>158</v>
-      </c>
-      <c r="AP20" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ20" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR20" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU20">
-        <v>1</v>
-      </c>
-      <c r="AV20" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW20" t="s">
-        <v>153</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>159</v>
-      </c>
       <c r="BB20" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="BC20" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B21" t="s">
         <v>55</v>
@@ -4055,7 +3890,7 @@
         <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E21" t="s">
         <v>57</v>
@@ -4082,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="M21">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>1E-4</v>
@@ -4097,10 +3932,13 @@
         <v>42</v>
       </c>
       <c r="R21" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="S21">
-        <v>800</v>
+        <v>4000</v>
+      </c>
+      <c r="T21">
+        <v>64</v>
       </c>
       <c r="U21">
         <v>2</v>
@@ -4109,81 +3947,87 @@
         <v>1800</v>
       </c>
       <c r="W21">
-        <v>1E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="X21">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0.3</v>
       </c>
       <c r="AB21" t="b">
         <v>1</v>
       </c>
       <c r="AC21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD21" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AE21" t="s">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="AF21" t="s">
         <v>62</v>
       </c>
       <c r="AG21" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AI21" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="AJ21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AL21" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AM21" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="AN21" t="s">
-        <v>178</v>
+        <v>122</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>185</v>
       </c>
       <c r="AP21" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>186</v>
+      </c>
+      <c r="AU21">
+        <v>1</v>
+      </c>
+      <c r="AV21" t="s">
         <v>68</v>
       </c>
-      <c r="AQ21" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR21" t="s">
-        <v>179</v>
-      </c>
-      <c r="AU21">
-        <v>1</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>71</v>
-      </c>
       <c r="AW21" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AX21" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="BA21" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="BB21" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="BC21" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B22" t="s">
         <v>55</v>
@@ -4192,7 +4036,7 @@
         <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E22" t="s">
         <v>57</v>
@@ -4219,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>1E-4</v>
@@ -4228,16 +4072,19 @@
         <v>1E-4</v>
       </c>
       <c r="P22" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="Q22">
         <v>42</v>
       </c>
       <c r="R22" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="S22">
-        <v>800</v>
+        <v>4000</v>
+      </c>
+      <c r="T22">
+        <v>64</v>
       </c>
       <c r="U22">
         <v>2</v>
@@ -4246,13 +4093,10 @@
         <v>1800</v>
       </c>
       <c r="W22">
-        <v>0.05</v>
+        <v>1E-3</v>
       </c>
       <c r="X22">
         <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0.1</v>
       </c>
       <c r="AB22" t="b">
         <v>1</v>
@@ -4261,69 +4105,72 @@
         <v>55</v>
       </c>
       <c r="AD22" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="AE22" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="AF22" t="s">
         <v>62</v>
       </c>
       <c r="AG22" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AI22" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="AJ22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AL22" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AM22" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="AN22" t="s">
-        <v>178</v>
+        <v>122</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>194</v>
       </c>
       <c r="AP22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="AQ22" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="AR22" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="AU22">
         <v>1</v>
       </c>
       <c r="AV22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AW22" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AX22" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="BA22" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="BB22" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="BC22" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="B23" t="s">
         <v>55</v>
@@ -4332,7 +4179,7 @@
         <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E23" t="s">
         <v>57</v>
@@ -4359,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>5.0000000000000001E-3</v>
@@ -4368,7 +4215,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="P23" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="Q23">
         <v>42</v>
@@ -4377,7 +4224,10 @@
         <v>59</v>
       </c>
       <c r="S23">
-        <v>800</v>
+        <v>4000</v>
+      </c>
+      <c r="T23">
+        <v>64</v>
       </c>
       <c r="U23">
         <v>2</v>
@@ -4386,84 +4236,87 @@
         <v>1800</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="X23">
         <v>0</v>
       </c>
       <c r="Y23">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AB23" t="b">
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD23" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="AE23" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="AF23" t="s">
         <v>62</v>
       </c>
       <c r="AG23" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AI23" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="AJ23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AL23" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AM23" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="AN23" t="s">
-        <v>178</v>
+        <v>122</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>194</v>
       </c>
       <c r="AP23" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>186</v>
+      </c>
+      <c r="AU23">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="s">
         <v>68</v>
       </c>
-      <c r="AQ23" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>179</v>
-      </c>
-      <c r="AU23">
-        <v>1</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>71</v>
-      </c>
       <c r="AW23" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AX23" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="BA23" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="BB23" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="BC23" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s">
         <v>55</v>
@@ -4472,7 +4325,7 @@
         <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="E24" t="s">
         <v>57</v>
@@ -4499,25 +4352,28 @@
         <v>1</v>
       </c>
       <c r="M24">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N24">
-        <v>0.01</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="O24">
-        <v>0.01</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="P24" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="Q24">
         <v>42</v>
       </c>
       <c r="R24" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="S24">
-        <v>800</v>
+        <v>3000</v>
+      </c>
+      <c r="T24">
+        <v>48</v>
       </c>
       <c r="U24">
         <v>2</v>
@@ -4529,10 +4385,7 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>0.9</v>
-      </c>
-      <c r="Y24">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="b">
         <v>1</v>
@@ -4541,69 +4394,72 @@
         <v>55</v>
       </c>
       <c r="AD24" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="AE24" t="s">
-        <v>61</v>
+        <v>207</v>
       </c>
       <c r="AF24" t="s">
         <v>62</v>
       </c>
       <c r="AG24" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="AI24" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>207</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>212</v>
+      </c>
+      <c r="AU24">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>208</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>213</v>
+      </c>
+      <c r="BA24" t="s">
         <v>188</v>
       </c>
-      <c r="AJ24" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>177</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP24" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>179</v>
-      </c>
-      <c r="AU24">
-        <v>1</v>
-      </c>
-      <c r="AV24" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>175</v>
-      </c>
-      <c r="AX24" t="s">
-        <v>180</v>
-      </c>
-      <c r="BA24" t="s">
-        <v>189</v>
-      </c>
       <c r="BB24" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="BC24" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
         <v>55</v>
@@ -4612,7 +4468,7 @@
         <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="E25" t="s">
         <v>57</v>
@@ -4639,25 +4495,28 @@
         <v>1</v>
       </c>
       <c r="M25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="N25">
-        <v>5.0000000000000001E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="O25">
-        <v>5.0000000000000001E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="P25" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="Q25">
         <v>42</v>
       </c>
       <c r="R25" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="S25">
-        <v>1500</v>
+        <v>3000</v>
+      </c>
+      <c r="T25">
+        <v>48</v>
       </c>
       <c r="U25">
         <v>2</v>
@@ -4666,1628 +4525,82 @@
         <v>1800</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
+      <c r="Y25">
+        <v>0.3</v>
+      </c>
       <c r="AB25" t="b">
         <v>1</v>
       </c>
       <c r="AC25" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD25" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="AE25" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="AF25" t="s">
         <v>62</v>
       </c>
       <c r="AG25" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="AI25" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="AJ25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AL25" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AM25" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="AN25" t="s">
-        <v>178</v>
+        <v>122</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>207</v>
       </c>
       <c r="AP25" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>212</v>
+      </c>
+      <c r="AU25">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="s">
         <v>68</v>
       </c>
-      <c r="AQ25" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR25" t="s">
-        <v>200</v>
-      </c>
-      <c r="AU25">
-        <v>1</v>
-      </c>
-      <c r="AV25" t="s">
-        <v>71</v>
-      </c>
       <c r="AW25" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="AX25" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="BA25" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="BB25" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="BC25" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>205</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" t="s">
-        <v>206</v>
-      </c>
-      <c r="E26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>8</v>
-      </c>
-      <c r="N26">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="O26">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="P26" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q26">
-        <v>42</v>
-      </c>
-      <c r="R26" t="s">
-        <v>90</v>
-      </c>
-      <c r="S26">
-        <v>1500</v>
-      </c>
-      <c r="U26">
-        <v>2</v>
-      </c>
-      <c r="V26">
-        <v>1800</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC26" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>195</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>196</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>198</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>199</v>
-      </c>
-      <c r="AM26" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP26" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ26" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>200</v>
-      </c>
-      <c r="AU26">
-        <v>1</v>
-      </c>
-      <c r="AV26" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AX26" t="s">
-        <v>201</v>
-      </c>
-      <c r="BA26" t="s">
-        <v>202</v>
-      </c>
-      <c r="BB26" t="s">
-        <v>203</v>
-      </c>
-      <c r="BC26" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>208</v>
-      </c>
-      <c r="B27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" t="s">
-        <v>209</v>
-      </c>
-      <c r="E27" t="s">
-        <v>57</v>
-      </c>
-      <c r="F27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <v>4</v>
-      </c>
-      <c r="N27">
-        <v>1E-3</v>
-      </c>
-      <c r="O27">
-        <v>1E-3</v>
-      </c>
-      <c r="P27" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q27">
-        <v>42</v>
-      </c>
-      <c r="R27" t="s">
-        <v>59</v>
-      </c>
-      <c r="S27">
-        <v>1500</v>
-      </c>
-      <c r="U27">
-        <v>2</v>
-      </c>
-      <c r="V27">
-        <v>1800</v>
-      </c>
-      <c r="W27">
-        <v>1E-3</v>
-      </c>
-      <c r="X27">
-        <v>0.9</v>
-      </c>
-      <c r="Y27">
-        <v>0.3</v>
-      </c>
-      <c r="AB27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>195</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>196</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>197</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>210</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK27" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL27" t="s">
-        <v>199</v>
-      </c>
-      <c r="AM27" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP27" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ27" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR27" t="s">
-        <v>200</v>
-      </c>
-      <c r="AU27">
-        <v>1</v>
-      </c>
-      <c r="AV27" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW27" t="s">
-        <v>197</v>
-      </c>
-      <c r="AX27" t="s">
-        <v>201</v>
-      </c>
-      <c r="BA27" t="s">
-        <v>211</v>
-      </c>
-      <c r="BB27" t="s">
-        <v>212</v>
-      </c>
-      <c r="BC27" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>213</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" t="s">
-        <v>214</v>
-      </c>
-      <c r="E28" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>4</v>
-      </c>
-      <c r="N28">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="O28">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="P28" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q28">
-        <v>42</v>
-      </c>
-      <c r="R28" t="s">
-        <v>90</v>
-      </c>
-      <c r="S28">
-        <v>1500</v>
-      </c>
-      <c r="U28">
-        <v>2</v>
-      </c>
-      <c r="V28">
-        <v>1800</v>
-      </c>
-      <c r="W28">
-        <v>1E-4</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>195</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>196</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>197</v>
-      </c>
-      <c r="AI28" t="s">
-        <v>210</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK28" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL28" t="s">
-        <v>199</v>
-      </c>
-      <c r="AM28" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP28" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ28" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR28" t="s">
-        <v>200</v>
-      </c>
-      <c r="AU28">
-        <v>1</v>
-      </c>
-      <c r="AV28" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW28" t="s">
-        <v>197</v>
-      </c>
-      <c r="AX28" t="s">
-        <v>201</v>
-      </c>
-      <c r="BA28" t="s">
-        <v>211</v>
-      </c>
-      <c r="BB28" t="s">
-        <v>212</v>
-      </c>
-      <c r="BC28" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
         <v>215</v>
-      </c>
-      <c r="B29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" t="s">
-        <v>216</v>
-      </c>
-      <c r="E29" t="s">
-        <v>57</v>
-      </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
-      <c r="M29">
-        <v>8</v>
-      </c>
-      <c r="N29">
-        <v>5.0000000000000002E-5</v>
-      </c>
-      <c r="O29">
-        <v>5.0000000000000002E-5</v>
-      </c>
-      <c r="P29" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q29">
-        <v>42</v>
-      </c>
-      <c r="R29" t="s">
-        <v>90</v>
-      </c>
-      <c r="S29">
-        <v>1200</v>
-      </c>
-      <c r="U29">
-        <v>2</v>
-      </c>
-      <c r="V29">
-        <v>1800</v>
-      </c>
-      <c r="W29">
-        <v>0.01</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>217</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>218</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI29" t="s">
-        <v>220</v>
-      </c>
-      <c r="AJ29" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK29" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>221</v>
-      </c>
-      <c r="AM29" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP29" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ29" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR29" t="s">
-        <v>222</v>
-      </c>
-      <c r="AU29">
-        <v>1</v>
-      </c>
-      <c r="AV29" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW29" t="s">
-        <v>219</v>
-      </c>
-      <c r="AX29" t="s">
-        <v>223</v>
-      </c>
-      <c r="BA29" t="s">
-        <v>224</v>
-      </c>
-      <c r="BB29" t="s">
-        <v>225</v>
-      </c>
-      <c r="BC29" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>227</v>
-      </c>
-      <c r="B30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" t="s">
-        <v>228</v>
-      </c>
-      <c r="E30" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-      <c r="M30">
-        <v>4</v>
-      </c>
-      <c r="N30">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="O30">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="P30" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q30">
-        <v>42</v>
-      </c>
-      <c r="R30" t="s">
-        <v>59</v>
-      </c>
-      <c r="S30">
-        <v>1200</v>
-      </c>
-      <c r="U30">
-        <v>2</v>
-      </c>
-      <c r="V30">
-        <v>1800</v>
-      </c>
-      <c r="W30">
-        <v>0.05</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0.3</v>
-      </c>
-      <c r="AB30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>217</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>218</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI30" t="s">
-        <v>220</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK30" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>221</v>
-      </c>
-      <c r="AM30" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP30" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ30" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR30" t="s">
-        <v>222</v>
-      </c>
-      <c r="AU30">
-        <v>1</v>
-      </c>
-      <c r="AV30" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW30" t="s">
-        <v>219</v>
-      </c>
-      <c r="AX30" t="s">
-        <v>223</v>
-      </c>
-      <c r="BA30" t="s">
-        <v>224</v>
-      </c>
-      <c r="BB30" t="s">
-        <v>225</v>
-      </c>
-      <c r="BC30" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>230</v>
-      </c>
-      <c r="B31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" t="s">
-        <v>231</v>
-      </c>
-      <c r="E31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>1</v>
-      </c>
-      <c r="M31">
-        <v>4</v>
-      </c>
-      <c r="N31">
-        <v>1E-4</v>
-      </c>
-      <c r="O31">
-        <v>1E-4</v>
-      </c>
-      <c r="P31" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q31">
-        <v>42</v>
-      </c>
-      <c r="R31" t="s">
-        <v>90</v>
-      </c>
-      <c r="S31">
-        <v>1200</v>
-      </c>
-      <c r="U31">
-        <v>2</v>
-      </c>
-      <c r="V31">
-        <v>1800</v>
-      </c>
-      <c r="W31">
-        <v>0.05</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>217</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>218</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI31" t="s">
-        <v>232</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>221</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP31" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ31" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR31" t="s">
-        <v>222</v>
-      </c>
-      <c r="AU31">
-        <v>1</v>
-      </c>
-      <c r="AV31" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW31" t="s">
-        <v>219</v>
-      </c>
-      <c r="AX31" t="s">
-        <v>223</v>
-      </c>
-      <c r="BA31" t="s">
-        <v>224</v>
-      </c>
-      <c r="BB31" t="s">
-        <v>233</v>
-      </c>
-      <c r="BC31" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>234</v>
-      </c>
-      <c r="B32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E32" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32">
-        <v>8</v>
-      </c>
-      <c r="N32">
-        <v>1E-4</v>
-      </c>
-      <c r="O32">
-        <v>1E-4</v>
-      </c>
-      <c r="P32" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q32">
-        <v>42</v>
-      </c>
-      <c r="R32" t="s">
-        <v>59</v>
-      </c>
-      <c r="S32">
-        <v>4000</v>
-      </c>
-      <c r="T32">
-        <v>64</v>
-      </c>
-      <c r="U32">
-        <v>2</v>
-      </c>
-      <c r="V32">
-        <v>1800</v>
-      </c>
-      <c r="W32">
-        <v>1E-4</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0.3</v>
-      </c>
-      <c r="AB32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>236</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>237</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>238</v>
-      </c>
-      <c r="AI32" t="s">
-        <v>239</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>76</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>240</v>
-      </c>
-      <c r="AM32" t="s">
-        <v>240</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>178</v>
-      </c>
-      <c r="AO32" t="s">
-        <v>241</v>
-      </c>
-      <c r="AP32" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ32" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR32" t="s">
-        <v>242</v>
-      </c>
-      <c r="AU32">
-        <v>1</v>
-      </c>
-      <c r="AV32" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW32" t="s">
-        <v>238</v>
-      </c>
-      <c r="AX32" t="s">
-        <v>243</v>
-      </c>
-      <c r="BA32" t="s">
-        <v>244</v>
-      </c>
-      <c r="BB32" t="s">
-        <v>245</v>
-      </c>
-      <c r="BC32" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="33" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>247</v>
-      </c>
-      <c r="B33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" t="s">
-        <v>248</v>
-      </c>
-      <c r="E33" t="s">
-        <v>57</v>
-      </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
-      <c r="M33">
-        <v>8</v>
-      </c>
-      <c r="N33">
-        <v>1E-4</v>
-      </c>
-      <c r="O33">
-        <v>1E-4</v>
-      </c>
-      <c r="P33" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q33">
-        <v>42</v>
-      </c>
-      <c r="R33" t="s">
-        <v>90</v>
-      </c>
-      <c r="S33">
-        <v>4000</v>
-      </c>
-      <c r="T33">
-        <v>64</v>
-      </c>
-      <c r="U33">
-        <v>2</v>
-      </c>
-      <c r="V33">
-        <v>1800</v>
-      </c>
-      <c r="W33">
-        <v>1E-3</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>249</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>250</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>238</v>
-      </c>
-      <c r="AI33" t="s">
-        <v>251</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK33" t="s">
-        <v>76</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>240</v>
-      </c>
-      <c r="AM33" t="s">
-        <v>240</v>
-      </c>
-      <c r="AN33" t="s">
-        <v>178</v>
-      </c>
-      <c r="AO33" t="s">
-        <v>250</v>
-      </c>
-      <c r="AP33" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ33" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR33" t="s">
-        <v>242</v>
-      </c>
-      <c r="AU33">
-        <v>1</v>
-      </c>
-      <c r="AV33" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW33" t="s">
-        <v>238</v>
-      </c>
-      <c r="AX33" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA33" t="s">
-        <v>253</v>
-      </c>
-      <c r="BB33" t="s">
-        <v>254</v>
-      </c>
-      <c r="BC33" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="34" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>256</v>
-      </c>
-      <c r="B34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" t="s">
-        <v>257</v>
-      </c>
-      <c r="E34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
-      <c r="L34">
-        <v>1</v>
-      </c>
-      <c r="M34">
-        <v>8</v>
-      </c>
-      <c r="N34">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="O34">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="P34" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q34">
-        <v>42</v>
-      </c>
-      <c r="R34" t="s">
-        <v>59</v>
-      </c>
-      <c r="S34">
-        <v>4000</v>
-      </c>
-      <c r="T34">
-        <v>64</v>
-      </c>
-      <c r="U34">
-        <v>2</v>
-      </c>
-      <c r="V34">
-        <v>1800</v>
-      </c>
-      <c r="W34">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0.3</v>
-      </c>
-      <c r="AB34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>249</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>250</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>238</v>
-      </c>
-      <c r="AI34" t="s">
-        <v>258</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK34" t="s">
-        <v>76</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>240</v>
-      </c>
-      <c r="AM34" t="s">
-        <v>240</v>
-      </c>
-      <c r="AN34" t="s">
-        <v>178</v>
-      </c>
-      <c r="AO34" t="s">
-        <v>250</v>
-      </c>
-      <c r="AP34" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ34" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR34" t="s">
-        <v>242</v>
-      </c>
-      <c r="AU34">
-        <v>1</v>
-      </c>
-      <c r="AV34" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW34" t="s">
-        <v>238</v>
-      </c>
-      <c r="AX34" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA34" t="s">
-        <v>253</v>
-      </c>
-      <c r="BB34" t="s">
-        <v>259</v>
-      </c>
-      <c r="BC34" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="35" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>260</v>
-      </c>
-      <c r="B35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" t="s">
-        <v>261</v>
-      </c>
-      <c r="E35" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
-      <c r="L35">
-        <v>1</v>
-      </c>
-      <c r="M35">
-        <v>32</v>
-      </c>
-      <c r="N35">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="O35">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="P35" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q35">
-        <v>42</v>
-      </c>
-      <c r="R35" t="s">
-        <v>90</v>
-      </c>
-      <c r="S35">
-        <v>3000</v>
-      </c>
-      <c r="T35">
-        <v>48</v>
-      </c>
-      <c r="U35">
-        <v>2</v>
-      </c>
-      <c r="V35">
-        <v>1800</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC35" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>262</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>263</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>264</v>
-      </c>
-      <c r="AI35" t="s">
-        <v>265</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>266</v>
-      </c>
-      <c r="AM35" t="s">
-        <v>267</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>178</v>
-      </c>
-      <c r="AO35" t="s">
-        <v>263</v>
-      </c>
-      <c r="AP35" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ35" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR35" t="s">
-        <v>268</v>
-      </c>
-      <c r="AU35">
-        <v>1</v>
-      </c>
-      <c r="AV35" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW35" t="s">
-        <v>264</v>
-      </c>
-      <c r="AX35" t="s">
-        <v>269</v>
-      </c>
-      <c r="BA35" t="s">
-        <v>244</v>
-      </c>
-      <c r="BB35" t="s">
-        <v>270</v>
-      </c>
-      <c r="BC35" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="36" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>272</v>
-      </c>
-      <c r="B36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" t="s">
-        <v>273</v>
-      </c>
-      <c r="E36" t="s">
-        <v>57</v>
-      </c>
-      <c r="F36" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="L36">
-        <v>1</v>
-      </c>
-      <c r="M36">
-        <v>32</v>
-      </c>
-      <c r="N36">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="O36">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="P36" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q36">
-        <v>42</v>
-      </c>
-      <c r="R36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S36">
-        <v>3000</v>
-      </c>
-      <c r="T36">
-        <v>48</v>
-      </c>
-      <c r="U36">
-        <v>2</v>
-      </c>
-      <c r="V36">
-        <v>1800</v>
-      </c>
-      <c r="W36">
-        <v>1E-3</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>0.3</v>
-      </c>
-      <c r="AB36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>262</v>
-      </c>
-      <c r="AE36" t="s">
-        <v>263</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>264</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>274</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK36" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>266</v>
-      </c>
-      <c r="AM36" t="s">
-        <v>267</v>
-      </c>
-      <c r="AN36" t="s">
-        <v>178</v>
-      </c>
-      <c r="AO36" t="s">
-        <v>263</v>
-      </c>
-      <c r="AP36" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ36" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR36" t="s">
-        <v>268</v>
-      </c>
-      <c r="AU36">
-        <v>1</v>
-      </c>
-      <c r="AV36" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW36" t="s">
-        <v>264</v>
-      </c>
-      <c r="AX36" t="s">
-        <v>269</v>
-      </c>
-      <c r="BA36" t="s">
-        <v>275</v>
-      </c>
-      <c r="BB36" t="s">
-        <v>276</v>
-      </c>
-      <c r="BC36" t="s">
-        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/run_manifest.xlsx
+++ b/outputs/run_manifest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://curtin-my.sharepoint.com/personal/21550803_student_curtin_edu_au/Documents/Documents/University/MLaaS/MLaaS-Dataset-Generator/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_6435B315D57BF36E2FFA2211595ED87656CC8980" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78007087-503D-4620-8461-6AAA465375DC}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_6435B315D57BF36E2FFA2211595ED87656CC8980" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14D0CB5-4BC1-42CE-8B33-564D1DDAB910}"/>
   <bookViews>
-    <workbookView xWindow="-23955" yWindow="4140" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="runs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="163">
   <si>
     <t>external_run_id</t>
   </si>
@@ -223,9 +223,6 @@
     <t>task_head</t>
   </si>
   <si>
-    <t>single_text</t>
-  </si>
-  <si>
     <t>registry_curated</t>
   </si>
   <si>
@@ -247,129 +244,9 @@
     <t>adamw</t>
   </si>
   <si>
-    <t>wikitext</t>
-  </si>
-  <si>
-    <t>wikitext-2-raw-v1</t>
-  </si>
-  <si>
-    <t>hf_textgen_000017</t>
-  </si>
-  <si>
-    <t>distilgpt2__wikitext2_lm__finetune_transfer__v0</t>
-  </si>
-  <si>
-    <t>causal_lm_generation</t>
-  </si>
-  <si>
-    <t>distilgpt2</t>
-  </si>
-  <si>
-    <t>language-modeling</t>
-  </si>
-  <si>
-    <t>text-generation</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/distilgpt2</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "text_generation", "run_regime": "finetune_transfer", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_textgen_000018</t>
-  </si>
-  <si>
-    <t>distilgpt2__wikitext2_lm__inference_only__v0</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "text_generation", "run_regime": "inference_only", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_textgen_000019</t>
-  </si>
-  <si>
-    <t>gpt2__wikitext2_lm__finetune_transfer__v0</t>
-  </si>
-  <si>
-    <t>gpt2</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/gpt2</t>
-  </si>
-  <si>
-    <t>hf_textgen_000020</t>
-  </si>
-  <si>
-    <t>gpt2__wikitext2_lm__inference_only__v0</t>
-  </si>
-  <si>
-    <t>hf_text2text_000021</t>
-  </si>
-  <si>
-    <t>google_flan-t5-small__cnn_dailymail__finetune_transfer__v0</t>
-  </si>
-  <si>
-    <t>seq2seq_generation</t>
-  </si>
-  <si>
-    <t>cnn_dailymail</t>
-  </si>
-  <si>
-    <t>3.0.0</t>
-  </si>
-  <si>
-    <t>google/flan-t5-small</t>
-  </si>
-  <si>
-    <t>highlights</t>
-  </si>
-  <si>
-    <t>article</t>
-  </si>
-  <si>
-    <t>summarization</t>
-  </si>
-  <si>
-    <t>text2text-generation</t>
-  </si>
-  <si>
     <t>google</t>
   </si>
   <si>
-    <t>https://huggingface.co/google/flan-t5-small</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "text2text_generation", "run_regime": "finetune_transfer", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_text2text_000022</t>
-  </si>
-  <si>
-    <t>google_flan-t5-small__cnn_dailymail__inference_only__v0</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "text2text_generation", "run_regime": "inference_only", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_text2text_000023</t>
-  </si>
-  <si>
-    <t>t5-small__cnn_dailymail__finetune_transfer__v0</t>
-  </si>
-  <si>
-    <t>t5-small</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/t5-small</t>
-  </si>
-  <si>
-    <t>hf_text2text_000024</t>
-  </si>
-  <si>
-    <t>t5-small__cnn_dailymail__inference_only__v0</t>
-  </si>
-  <si>
     <t>hf_imgcls_000025</t>
   </si>
   <si>
@@ -632,57 +509,6 @@
   </si>
   <si>
     <t>https://huggingface.co/openai/clip-vit-large-patch14</t>
-  </si>
-  <si>
-    <t>hf_vqa_000039</t>
-  </si>
-  <si>
-    <t>Salesforce_blip-vqa-base__vqav2__inference_only__v0</t>
-  </si>
-  <si>
-    <t>visual_question_answering</t>
-  </si>
-  <si>
-    <t>vqa</t>
-  </si>
-  <si>
-    <t>HuggingFaceM4/VQAv2</t>
-  </si>
-  <si>
-    <t>Salesforce/blip-vqa-base</t>
-  </si>
-  <si>
-    <t>answers</t>
-  </si>
-  <si>
-    <t>question</t>
-  </si>
-  <si>
-    <t>image_question_answer</t>
-  </si>
-  <si>
-    <t>visual-question-answering</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/Salesforce/blip-vqa-base</t>
-  </si>
-  <si>
-    <t>{"source": "registry", "registry_task": "visual_question_answering", "run_regime": "inference_only", "audit_json_used": false, "dataset_pairing_source": "registry.dataset_keys"}</t>
-  </si>
-  <si>
-    <t>hf_vqa_000040</t>
-  </si>
-  <si>
-    <t>dandelin_vilt-b32-finetuned-vqa__vqav2__inference_only__v0</t>
-  </si>
-  <si>
-    <t>dandelin/vilt-b32-finetuned-vqa</t>
-  </si>
-  <si>
-    <t>dandelin</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/dandelin/vilt-b32-finetuned-vqa</t>
   </si>
 </sst>
 </file>
@@ -1049,8 +875,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BC25"/>
+  <dimension ref="A1:BC15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1221,7 +1050,7 @@
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -1230,7 +1059,7 @@
         <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>57</v>
@@ -1257,28 +1086,25 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N2">
-        <v>2.0000000000000002E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="O2">
-        <v>2.0000000000000002E-5</v>
+        <v>1E-4</v>
       </c>
       <c r="P2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="Q2">
         <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S2">
-        <v>1000</v>
-      </c>
-      <c r="T2">
-        <v>256</v>
+        <v>800</v>
       </c>
       <c r="U2">
         <v>2</v>
@@ -1287,10 +1113,10 @@
         <v>1800</v>
       </c>
       <c r="W2">
-        <v>0.05</v>
+        <v>1E-3</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AB2" t="b">
         <v>1</v>
@@ -1299,7 +1125,7 @@
         <v>60</v>
       </c>
       <c r="AD2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AE2" t="s">
         <v>61</v>
@@ -1308,13 +1134,10 @@
         <v>62</v>
       </c>
       <c r="AG2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ2" t="s">
         <v>63</v>
@@ -1323,12 +1146,12 @@
         <v>64</v>
       </c>
       <c r="AL2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="s">
         <v>62</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AN2" t="s">
         <v>81</v>
       </c>
       <c r="AP2" t="s">
@@ -1338,30 +1161,33 @@
         <v>66</v>
       </c>
       <c r="AR2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="s">
         <v>67</v>
       </c>
-      <c r="AU2">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>68</v>
-      </c>
       <c r="AW2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AX2" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>74</v>
       </c>
       <c r="BB2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BC2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -1370,7 +1196,7 @@
         <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>57</v>
@@ -1397,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N3">
         <v>1E-4</v>
@@ -1406,7 +1232,7 @@
         <v>1E-4</v>
       </c>
       <c r="P3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q3">
         <v>42</v>
@@ -1415,10 +1241,7 @@
         <v>59</v>
       </c>
       <c r="S3">
-        <v>1000</v>
-      </c>
-      <c r="T3">
-        <v>256</v>
+        <v>800</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1427,13 +1250,13 @@
         <v>1800</v>
       </c>
       <c r="W3">
-        <v>1E-3</v>
+        <v>0.05</v>
       </c>
       <c r="X3">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="AB3" t="b">
         <v>1</v>
@@ -1442,7 +1265,7 @@
         <v>55</v>
       </c>
       <c r="AD3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AE3" t="s">
         <v>61</v>
@@ -1451,13 +1274,10 @@
         <v>62</v>
       </c>
       <c r="AG3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AI3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ3" t="s">
         <v>63</v>
@@ -1466,45 +1286,48 @@
         <v>64</v>
       </c>
       <c r="AL3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="s">
         <v>62</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AN3" t="s">
         <v>81</v>
       </c>
       <c r="AP3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>69</v>
       </c>
-      <c r="AQ3" t="s">
-        <v>70</v>
-      </c>
       <c r="AR3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU3">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="s">
         <v>67</v>
       </c>
-      <c r="AU3">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>68</v>
-      </c>
       <c r="AW3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AX3" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>74</v>
       </c>
       <c r="BB3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BC3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -1513,7 +1336,7 @@
         <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>57</v>
@@ -1540,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N4">
         <v>5.0000000000000001E-3</v>
@@ -1549,19 +1372,16 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q4">
         <v>42</v>
       </c>
       <c r="R4" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="S4">
-        <v>1000</v>
-      </c>
-      <c r="T4">
-        <v>256</v>
+        <v>800</v>
       </c>
       <c r="U4">
         <v>2</v>
@@ -1573,7 +1393,10 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0.1</v>
       </c>
       <c r="AB4" t="b">
         <v>1</v>
@@ -1582,7 +1405,7 @@
         <v>60</v>
       </c>
       <c r="AD4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AE4" t="s">
         <v>61</v>
@@ -1591,13 +1414,10 @@
         <v>62</v>
       </c>
       <c r="AG4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AJ4" t="s">
         <v>63</v>
@@ -1606,12 +1426,12 @@
         <v>64</v>
       </c>
       <c r="AL4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="s">
         <v>62</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AN4" t="s">
         <v>81</v>
       </c>
       <c r="AP4" t="s">
@@ -1621,30 +1441,33 @@
         <v>66</v>
       </c>
       <c r="AR4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU4">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="s">
         <v>67</v>
       </c>
-      <c r="AU4">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>68</v>
-      </c>
       <c r="AW4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AX4" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>92</v>
       </c>
       <c r="BB4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="BC4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -1653,7 +1476,7 @@
         <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>57</v>
@@ -1680,28 +1503,25 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N5">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="O5">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="P5" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="Q5">
         <v>42</v>
       </c>
       <c r="R5" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="S5">
-        <v>1000</v>
-      </c>
-      <c r="T5">
-        <v>256</v>
+        <v>800</v>
       </c>
       <c r="U5">
         <v>2</v>
@@ -1715,6 +1535,9 @@
       <c r="X5">
         <v>0.9</v>
       </c>
+      <c r="Y5">
+        <v>0.1</v>
+      </c>
       <c r="AB5" t="b">
         <v>1</v>
       </c>
@@ -1722,7 +1545,7 @@
         <v>55</v>
       </c>
       <c r="AD5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AE5" t="s">
         <v>61</v>
@@ -1731,13 +1554,10 @@
         <v>62</v>
       </c>
       <c r="AG5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AJ5" t="s">
         <v>63</v>
@@ -1746,45 +1566,48 @@
         <v>64</v>
       </c>
       <c r="AL5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="s">
         <v>62</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AN5" t="s">
         <v>81</v>
       </c>
       <c r="AP5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ5" t="s">
         <v>69</v>
       </c>
-      <c r="AQ5" t="s">
-        <v>70</v>
-      </c>
       <c r="AR5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU5">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="s">
         <v>67</v>
       </c>
-      <c r="AU5">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>68</v>
-      </c>
       <c r="AW5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AX5" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>92</v>
       </c>
       <c r="BB5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="BC5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -1793,7 +1616,7 @@
         <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
         <v>57</v>
@@ -1820,28 +1643,25 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="N6">
-        <v>1E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="O6">
-        <v>1E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q6">
         <v>42</v>
       </c>
       <c r="R6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S6">
-        <v>1000</v>
-      </c>
-      <c r="T6">
-        <v>256</v>
+        <v>1500</v>
       </c>
       <c r="U6">
         <v>2</v>
@@ -1850,10 +1670,10 @@
         <v>1800</v>
       </c>
       <c r="W6">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="b">
         <v>1</v>
@@ -1862,22 +1682,19 @@
         <v>60</v>
       </c>
       <c r="AD6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE6" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="AF6" t="s">
         <v>62</v>
       </c>
       <c r="AG6" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AI6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AJ6" t="s">
         <v>63</v>
@@ -1886,13 +1703,13 @@
         <v>64</v>
       </c>
       <c r="AL6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AM6" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>102</v>
+        <v>62</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>81</v>
       </c>
       <c r="AP6" t="s">
         <v>65</v>
@@ -1901,33 +1718,33 @@
         <v>66</v>
       </c>
       <c r="AR6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="s">
         <v>67</v>
       </c>
-      <c r="AU6">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>68</v>
-      </c>
       <c r="AW6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AX6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BB6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BC6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -1936,7 +1753,7 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>57</v>
@@ -1963,28 +1780,25 @@
         <v>1</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>2.0000000000000002E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="O7">
-        <v>2.0000000000000002E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q7">
         <v>42</v>
       </c>
       <c r="R7" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="S7">
-        <v>1000</v>
-      </c>
-      <c r="T7">
-        <v>256</v>
+        <v>1500</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -1993,14 +1807,11 @@
         <v>1800</v>
       </c>
       <c r="W7">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
-      <c r="Y7">
-        <v>0.3</v>
-      </c>
       <c r="AB7" t="b">
         <v>1</v>
       </c>
@@ -2008,22 +1819,19 @@
         <v>55</v>
       </c>
       <c r="AD7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE7" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="AF7" t="s">
         <v>62</v>
       </c>
       <c r="AG7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AI7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AJ7" t="s">
         <v>63</v>
@@ -2032,48 +1840,48 @@
         <v>64</v>
       </c>
       <c r="AL7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU7">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW7" t="s">
         <v>100</v>
       </c>
-      <c r="AM7" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>102</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AU7">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>97</v>
-      </c>
       <c r="AX7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BB7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BC7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
         <v>55</v>
@@ -2082,7 +1890,7 @@
         <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>57</v>
@@ -2109,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="O8">
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="P8" t="s">
         <v>58</v>
@@ -2127,10 +1935,7 @@
         <v>59</v>
       </c>
       <c r="S8">
-        <v>1000</v>
-      </c>
-      <c r="T8">
-        <v>256</v>
+        <v>1500</v>
       </c>
       <c r="U8">
         <v>2</v>
@@ -2139,13 +1944,13 @@
         <v>1800</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Y8">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AB8" t="b">
         <v>1</v>
@@ -2154,22 +1959,19 @@
         <v>60</v>
       </c>
       <c r="AD8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE8" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="AF8" t="s">
         <v>62</v>
       </c>
       <c r="AG8" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AI8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ8" t="s">
         <v>63</v>
@@ -2178,13 +1980,13 @@
         <v>64</v>
       </c>
       <c r="AL8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AM8" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>102</v>
+        <v>62</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>81</v>
       </c>
       <c r="AP8" t="s">
         <v>65</v>
@@ -2193,30 +1995,33 @@
         <v>66</v>
       </c>
       <c r="AR8" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="s">
         <v>67</v>
       </c>
-      <c r="AU8">
-        <v>1</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>68</v>
-      </c>
       <c r="AW8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AX8" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>114</v>
       </c>
       <c r="BB8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BC8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
         <v>55</v>
@@ -2225,7 +2030,7 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
         <v>57</v>
@@ -2252,28 +2057,25 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>1.0000000000000001E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="O9">
-        <v>1.0000000000000001E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="Q9">
         <v>42</v>
       </c>
       <c r="R9" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="S9">
-        <v>1000</v>
-      </c>
-      <c r="T9">
-        <v>256</v>
+        <v>1500</v>
       </c>
       <c r="U9">
         <v>2</v>
@@ -2282,14 +2084,11 @@
         <v>1800</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="X9">
         <v>0</v>
       </c>
-      <c r="Y9">
-        <v>0.1</v>
-      </c>
       <c r="AB9" t="b">
         <v>1</v>
       </c>
@@ -2297,22 +2096,19 @@
         <v>55</v>
       </c>
       <c r="AD9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE9" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="AF9" t="s">
         <v>62</v>
       </c>
       <c r="AG9" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AI9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ9" t="s">
         <v>63</v>
@@ -2321,45 +2117,48 @@
         <v>64</v>
       </c>
       <c r="AL9" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU9">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW9" t="s">
         <v>100</v>
       </c>
-      <c r="AM9" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>102</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AU9">
-        <v>1</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>97</v>
-      </c>
       <c r="AX9" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>114</v>
       </c>
       <c r="BB9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BC9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
@@ -2368,7 +2167,7 @@
         <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
         <v>57</v>
@@ -2395,25 +2194,25 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>1E-4</v>
+        <v>5.0000000000000002E-5</v>
       </c>
       <c r="O10">
-        <v>1E-4</v>
+        <v>5.0000000000000002E-5</v>
       </c>
       <c r="P10" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q10">
         <v>42</v>
       </c>
       <c r="R10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S10">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="U10">
         <v>2</v>
@@ -2422,10 +2221,10 @@
         <v>1800</v>
       </c>
       <c r="W10">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="X10">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="b">
         <v>1</v>
@@ -2434,19 +2233,19 @@
         <v>60</v>
       </c>
       <c r="AD10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AE10" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="AF10" t="s">
         <v>62</v>
       </c>
       <c r="AG10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AI10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AJ10" t="s">
         <v>63</v>
@@ -2455,13 +2254,13 @@
         <v>64</v>
       </c>
       <c r="AL10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AM10" t="s">
         <v>62</v>
       </c>
       <c r="AN10" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="AP10" t="s">
         <v>65</v>
@@ -2470,33 +2269,33 @@
         <v>66</v>
       </c>
       <c r="AR10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AU10">
         <v>1</v>
       </c>
       <c r="AV10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AW10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AX10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BA10" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="BB10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="BC10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
@@ -2505,7 +2304,7 @@
         <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
         <v>57</v>
@@ -2535,13 +2334,13 @@
         <v>4</v>
       </c>
       <c r="N11">
-        <v>1E-4</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="O11">
-        <v>1E-4</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q11">
         <v>42</v>
@@ -2550,7 +2349,7 @@
         <v>59</v>
       </c>
       <c r="S11">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="U11">
         <v>2</v>
@@ -2565,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AB11" t="b">
         <v>1</v>
@@ -2574,19 +2373,19 @@
         <v>55</v>
       </c>
       <c r="AD11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AE11" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="AF11" t="s">
         <v>62</v>
       </c>
       <c r="AG11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AI11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AJ11" t="s">
         <v>63</v>
@@ -2595,48 +2394,48 @@
         <v>64</v>
       </c>
       <c r="AL11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AM11" t="s">
         <v>62</v>
       </c>
       <c r="AN11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AU11">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW11" t="s">
         <v>122</v>
       </c>
-      <c r="AP11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>123</v>
-      </c>
-      <c r="AU11">
-        <v>1</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>119</v>
-      </c>
       <c r="AX11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BA11" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="BB11" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="BC11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
@@ -2645,7 +2444,7 @@
         <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
         <v>57</v>
@@ -2675,22 +2474,22 @@
         <v>4</v>
       </c>
       <c r="N12">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="O12">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="P12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q12">
         <v>42</v>
       </c>
       <c r="R12" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="S12">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -2699,34 +2498,31 @@
         <v>1800</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="X12">
         <v>0</v>
       </c>
-      <c r="Y12">
-        <v>0.1</v>
-      </c>
       <c r="AB12" t="b">
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AE12" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="AF12" t="s">
         <v>62</v>
       </c>
       <c r="AG12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AI12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AJ12" t="s">
         <v>63</v>
@@ -2735,48 +2531,48 @@
         <v>64</v>
       </c>
       <c r="AL12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AM12" t="s">
         <v>62</v>
       </c>
       <c r="AN12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>125</v>
+      </c>
+      <c r="AU12">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW12" t="s">
         <v>122</v>
       </c>
-      <c r="AP12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>123</v>
-      </c>
-      <c r="AU12">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>119</v>
-      </c>
       <c r="AX12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BA12" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="BB12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BC12" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B13" t="s">
         <v>55</v>
@@ -2785,7 +2581,7 @@
         <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
         <v>57</v>
@@ -2815,13 +2611,13 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
       <c r="O13">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
       <c r="P13" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="Q13">
         <v>42</v>
@@ -2830,7 +2626,10 @@
         <v>59</v>
       </c>
       <c r="S13">
-        <v>800</v>
+        <v>4000</v>
+      </c>
+      <c r="T13">
+        <v>64</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -2839,13 +2638,13 @@
         <v>1800</v>
       </c>
       <c r="W13">
+        <v>1E-4</v>
+      </c>
+      <c r="X13">
         <v>0</v>
       </c>
-      <c r="X13">
-        <v>0.9</v>
-      </c>
       <c r="Y13">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AB13" t="b">
         <v>1</v>
@@ -2854,69 +2653,72 @@
         <v>55</v>
       </c>
       <c r="AD13" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="AE13" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="AF13" t="s">
         <v>62</v>
       </c>
       <c r="AG13" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="AI13" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="AJ13" t="s">
         <v>63</v>
       </c>
       <c r="AK13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="AL13" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="AM13" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="AN13" t="s">
-        <v>122</v>
+        <v>81</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>144</v>
       </c>
       <c r="AP13" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ13" t="s">
         <v>69</v>
       </c>
-      <c r="AQ13" t="s">
-        <v>70</v>
-      </c>
       <c r="AR13" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="AU13">
         <v>1</v>
       </c>
       <c r="AV13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AW13" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="AX13" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="BA13" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="BB13" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="BC13" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
         <v>55</v>
@@ -2925,7 +2727,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
         <v>57</v>
@@ -2952,25 +2754,28 @@
         <v>1</v>
       </c>
       <c r="M14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="O14">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="P14" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="Q14">
         <v>42</v>
       </c>
       <c r="R14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S14">
-        <v>1500</v>
+        <v>4000</v>
+      </c>
+      <c r="T14">
+        <v>64</v>
       </c>
       <c r="U14">
         <v>2</v>
@@ -2979,7 +2784,7 @@
         <v>1800</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="X14">
         <v>0</v>
@@ -2988,13 +2793,13 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AD14" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="AE14" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="AF14" t="s">
         <v>62</v>
@@ -3003,57 +2808,60 @@
         <v>141</v>
       </c>
       <c r="AI14" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="AJ14" t="s">
         <v>63</v>
       </c>
       <c r="AK14" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="AL14" t="s">
         <v>143</v>
       </c>
       <c r="AM14" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="AN14" t="s">
-        <v>122</v>
+        <v>81</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>153</v>
       </c>
       <c r="AP14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AQ14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AR14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AU14">
         <v>1</v>
       </c>
       <c r="AV14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AW14" t="s">
         <v>141</v>
       </c>
       <c r="AX14" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="BA14" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="BB14" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="BC14" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s">
         <v>55</v>
@@ -3062,7 +2870,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E15" t="s">
         <v>57</v>
@@ -3092,22 +2900,25 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>1.0000000000000001E-5</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="O15">
-        <v>1.0000000000000001E-5</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q15">
         <v>42</v>
       </c>
       <c r="R15" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="S15">
-        <v>1500</v>
+        <v>4000</v>
+      </c>
+      <c r="T15">
+        <v>64</v>
       </c>
       <c r="U15">
         <v>2</v>
@@ -3116,11 +2927,14 @@
         <v>1800</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
+      <c r="Y15">
+        <v>0.3</v>
+      </c>
       <c r="AB15" t="b">
         <v>1</v>
       </c>
@@ -3128,10 +2942,10 @@
         <v>55</v>
       </c>
       <c r="AD15" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="AE15" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="AF15" t="s">
         <v>62</v>
@@ -3140,1467 +2954,55 @@
         <v>141</v>
       </c>
       <c r="AI15" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="AJ15" t="s">
         <v>63</v>
       </c>
       <c r="AK15" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="AL15" t="s">
         <v>143</v>
       </c>
       <c r="AM15" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="AN15" t="s">
-        <v>122</v>
+        <v>81</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>153</v>
       </c>
       <c r="AP15" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ15" t="s">
         <v>69</v>
       </c>
-      <c r="AQ15" t="s">
-        <v>70</v>
-      </c>
       <c r="AR15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AU15">
         <v>1</v>
       </c>
       <c r="AV15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AW15" t="s">
         <v>141</v>
       </c>
       <c r="AX15" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="BA15" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="BB15" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="BC15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>152</v>
-      </c>
-      <c r="B16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>4</v>
-      </c>
-      <c r="N16">
-        <v>1E-3</v>
-      </c>
-      <c r="O16">
-        <v>1E-3</v>
-      </c>
-      <c r="P16" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q16">
-        <v>42</v>
-      </c>
-      <c r="R16" t="s">
-        <v>59</v>
-      </c>
-      <c r="S16">
-        <v>1500</v>
-      </c>
-      <c r="U16">
-        <v>2</v>
-      </c>
-      <c r="V16">
-        <v>1800</v>
-      </c>
-      <c r="W16">
-        <v>1E-3</v>
-      </c>
-      <c r="X16">
-        <v>0.9</v>
-      </c>
-      <c r="Y16">
-        <v>0.3</v>
-      </c>
-      <c r="AB16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>140</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>141</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>154</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>143</v>
-      </c>
-      <c r="AM16" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP16" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ16" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>144</v>
-      </c>
-      <c r="AU16">
-        <v>1</v>
-      </c>
-      <c r="AV16" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW16" t="s">
-        <v>141</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>145</v>
-      </c>
-      <c r="BA16" t="s">
-        <v>155</v>
-      </c>
-      <c r="BB16" t="s">
-        <v>156</v>
-      </c>
-      <c r="BC16" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
         <v>158</v>
-      </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>4</v>
-      </c>
-      <c r="N17">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="O17">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="P17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q17">
-        <v>42</v>
-      </c>
-      <c r="R17" t="s">
-        <v>73</v>
-      </c>
-      <c r="S17">
-        <v>1500</v>
-      </c>
-      <c r="U17">
-        <v>2</v>
-      </c>
-      <c r="V17">
-        <v>1800</v>
-      </c>
-      <c r="W17">
-        <v>1E-4</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>140</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>141</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>154</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>143</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ17" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>144</v>
-      </c>
-      <c r="AU17">
-        <v>1</v>
-      </c>
-      <c r="AV17" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW17" t="s">
-        <v>141</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>145</v>
-      </c>
-      <c r="BA17" t="s">
-        <v>155</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>156</v>
-      </c>
-      <c r="BC17" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>8</v>
-      </c>
-      <c r="N18">
-        <v>5.0000000000000002E-5</v>
-      </c>
-      <c r="O18">
-        <v>5.0000000000000002E-5</v>
-      </c>
-      <c r="P18" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q18">
-        <v>42</v>
-      </c>
-      <c r="R18" t="s">
-        <v>73</v>
-      </c>
-      <c r="S18">
-        <v>1200</v>
-      </c>
-      <c r="U18">
-        <v>2</v>
-      </c>
-      <c r="V18">
-        <v>1800</v>
-      </c>
-      <c r="W18">
-        <v>0.01</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>164</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>165</v>
-      </c>
-      <c r="AM18" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ18" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>166</v>
-      </c>
-      <c r="AU18">
-        <v>1</v>
-      </c>
-      <c r="AV18" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW18" t="s">
-        <v>163</v>
-      </c>
-      <c r="AX18" t="s">
-        <v>167</v>
-      </c>
-      <c r="BA18" t="s">
-        <v>168</v>
-      </c>
-      <c r="BB18" t="s">
-        <v>169</v>
-      </c>
-      <c r="BC18" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>171</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>172</v>
-      </c>
-      <c r="E19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>4</v>
-      </c>
-      <c r="N19">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="O19">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="P19" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q19">
-        <v>42</v>
-      </c>
-      <c r="R19" t="s">
-        <v>59</v>
-      </c>
-      <c r="S19">
-        <v>1200</v>
-      </c>
-      <c r="U19">
-        <v>2</v>
-      </c>
-      <c r="V19">
-        <v>1800</v>
-      </c>
-      <c r="W19">
-        <v>0.05</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0.3</v>
-      </c>
-      <c r="AB19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>164</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>165</v>
-      </c>
-      <c r="AM19" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP19" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>166</v>
-      </c>
-      <c r="AU19">
-        <v>1</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW19" t="s">
-        <v>163</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>167</v>
-      </c>
-      <c r="BA19" t="s">
-        <v>168</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>169</v>
-      </c>
-      <c r="BC19" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>174</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>4</v>
-      </c>
-      <c r="N20">
-        <v>1E-4</v>
-      </c>
-      <c r="O20">
-        <v>1E-4</v>
-      </c>
-      <c r="P20" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q20">
-        <v>42</v>
-      </c>
-      <c r="R20" t="s">
-        <v>73</v>
-      </c>
-      <c r="S20">
-        <v>1200</v>
-      </c>
-      <c r="U20">
-        <v>2</v>
-      </c>
-      <c r="V20">
-        <v>1800</v>
-      </c>
-      <c r="W20">
-        <v>0.05</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>176</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>165</v>
-      </c>
-      <c r="AM20" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP20" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ20" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR20" t="s">
-        <v>166</v>
-      </c>
-      <c r="AU20">
-        <v>1</v>
-      </c>
-      <c r="AV20" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW20" t="s">
-        <v>163</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>167</v>
-      </c>
-      <c r="BA20" t="s">
-        <v>168</v>
-      </c>
-      <c r="BB20" t="s">
-        <v>177</v>
-      </c>
-      <c r="BC20" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" t="s">
-        <v>179</v>
-      </c>
-      <c r="E21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>8</v>
-      </c>
-      <c r="N21">
-        <v>1E-4</v>
-      </c>
-      <c r="O21">
-        <v>1E-4</v>
-      </c>
-      <c r="P21" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q21">
-        <v>42</v>
-      </c>
-      <c r="R21" t="s">
-        <v>59</v>
-      </c>
-      <c r="S21">
-        <v>4000</v>
-      </c>
-      <c r="T21">
-        <v>64</v>
-      </c>
-      <c r="U21">
-        <v>2</v>
-      </c>
-      <c r="V21">
-        <v>1800</v>
-      </c>
-      <c r="W21">
-        <v>1E-4</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0.3</v>
-      </c>
-      <c r="AB21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>181</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>183</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL21" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM21" t="s">
-        <v>184</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>185</v>
-      </c>
-      <c r="AP21" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ21" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR21" t="s">
-        <v>186</v>
-      </c>
-      <c r="AU21">
-        <v>1</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW21" t="s">
-        <v>182</v>
-      </c>
-      <c r="AX21" t="s">
-        <v>187</v>
-      </c>
-      <c r="BA21" t="s">
-        <v>188</v>
-      </c>
-      <c r="BB21" t="s">
-        <v>189</v>
-      </c>
-      <c r="BC21" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="22" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" t="s">
-        <v>192</v>
-      </c>
-      <c r="E22" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>8</v>
-      </c>
-      <c r="N22">
-        <v>1E-4</v>
-      </c>
-      <c r="O22">
-        <v>1E-4</v>
-      </c>
-      <c r="P22" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q22">
-        <v>42</v>
-      </c>
-      <c r="R22" t="s">
-        <v>73</v>
-      </c>
-      <c r="S22">
-        <v>4000</v>
-      </c>
-      <c r="T22">
-        <v>64</v>
-      </c>
-      <c r="U22">
-        <v>2</v>
-      </c>
-      <c r="V22">
-        <v>1800</v>
-      </c>
-      <c r="W22">
-        <v>1E-3</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>193</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>194</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>195</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM22" t="s">
-        <v>184</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO22" t="s">
-        <v>194</v>
-      </c>
-      <c r="AP22" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ22" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR22" t="s">
-        <v>186</v>
-      </c>
-      <c r="AU22">
-        <v>1</v>
-      </c>
-      <c r="AV22" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW22" t="s">
-        <v>182</v>
-      </c>
-      <c r="AX22" t="s">
-        <v>196</v>
-      </c>
-      <c r="BA22" t="s">
-        <v>197</v>
-      </c>
-      <c r="BB22" t="s">
-        <v>198</v>
-      </c>
-      <c r="BC22" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>200</v>
-      </c>
-      <c r="B23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" t="s">
-        <v>201</v>
-      </c>
-      <c r="E23" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="M23">
-        <v>8</v>
-      </c>
-      <c r="N23">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="O23">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="P23" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q23">
-        <v>42</v>
-      </c>
-      <c r="R23" t="s">
-        <v>59</v>
-      </c>
-      <c r="S23">
-        <v>4000</v>
-      </c>
-      <c r="T23">
-        <v>64</v>
-      </c>
-      <c r="U23">
-        <v>2</v>
-      </c>
-      <c r="V23">
-        <v>1800</v>
-      </c>
-      <c r="W23">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0.3</v>
-      </c>
-      <c r="AB23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>193</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>194</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>202</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK23" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL23" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM23" t="s">
-        <v>184</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO23" t="s">
-        <v>194</v>
-      </c>
-      <c r="AP23" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ23" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>186</v>
-      </c>
-      <c r="AU23">
-        <v>1</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW23" t="s">
-        <v>182</v>
-      </c>
-      <c r="AX23" t="s">
-        <v>196</v>
-      </c>
-      <c r="BA23" t="s">
-        <v>197</v>
-      </c>
-      <c r="BB23" t="s">
-        <v>203</v>
-      </c>
-      <c r="BC23" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>204</v>
-      </c>
-      <c r="B24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" t="s">
-        <v>205</v>
-      </c>
-      <c r="E24" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>32</v>
-      </c>
-      <c r="N24">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="O24">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="P24" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q24">
-        <v>42</v>
-      </c>
-      <c r="R24" t="s">
-        <v>73</v>
-      </c>
-      <c r="S24">
-        <v>3000</v>
-      </c>
-      <c r="T24">
-        <v>48</v>
-      </c>
-      <c r="U24">
-        <v>2</v>
-      </c>
-      <c r="V24">
-        <v>1800</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>206</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>210</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>211</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO24" t="s">
-        <v>207</v>
-      </c>
-      <c r="AP24" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>212</v>
-      </c>
-      <c r="AU24">
-        <v>1</v>
-      </c>
-      <c r="AV24" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>208</v>
-      </c>
-      <c r="AX24" t="s">
-        <v>213</v>
-      </c>
-      <c r="BA24" t="s">
-        <v>188</v>
-      </c>
-      <c r="BB24" t="s">
-        <v>214</v>
-      </c>
-      <c r="BC24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>216</v>
-      </c>
-      <c r="B25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" t="s">
-        <v>217</v>
-      </c>
-      <c r="E25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>32</v>
-      </c>
-      <c r="N25">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="O25">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="P25" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q25">
-        <v>42</v>
-      </c>
-      <c r="R25" t="s">
-        <v>59</v>
-      </c>
-      <c r="S25">
-        <v>3000</v>
-      </c>
-      <c r="T25">
-        <v>48</v>
-      </c>
-      <c r="U25">
-        <v>2</v>
-      </c>
-      <c r="V25">
-        <v>1800</v>
-      </c>
-      <c r="W25">
-        <v>1E-3</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0.3</v>
-      </c>
-      <c r="AB25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>206</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI25" t="s">
-        <v>218</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>210</v>
-      </c>
-      <c r="AM25" t="s">
-        <v>211</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO25" t="s">
-        <v>207</v>
-      </c>
-      <c r="AP25" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AU25">
-        <v>1</v>
-      </c>
-      <c r="AV25" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW25" t="s">
-        <v>208</v>
-      </c>
-      <c r="AX25" t="s">
-        <v>213</v>
-      </c>
-      <c r="BA25" t="s">
-        <v>219</v>
-      </c>
-      <c r="BB25" t="s">
-        <v>220</v>
-      </c>
-      <c r="BC25" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/run_manifest.xlsx
+++ b/outputs/run_manifest.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL25"/>
+  <dimension ref="A1:CQ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,140 +742,165 @@
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
+          <t>perturbation_stage_logging</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>perturbation_progress_logging</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
           <t>perturbation_sample_count</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>perturbation_candidate_units</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>perturbation_target_units</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>perturbation_trust_trials</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>perturbation_progress_sample_interval</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>perturbation_random_strength</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>explainability_method</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>explainability_target</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>service_source</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>model_role</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>fit_decision</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>fit_reason</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>realism_score</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>domain_alignment</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>dataset_hint</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>hf_pipeline_tag</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>hf_downloads</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>hf_likes</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>hf_dataset_id</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>downloads</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>likes</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>model_size</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>params_count</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>pipeline_tag</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>library_name</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>license</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>last_modified</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>hf_author</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>hf_url</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>hf_service_meta_json</t>
         </is>
@@ -979,7 +1004,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 0.0001, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.0001, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1070,58 +1095,68 @@
       <c r="BJ2" t="b">
         <v>1</v>
       </c>
-      <c r="BK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL2" t="n">
+      <c r="BK2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN2" t="n">
         <v>4</v>
       </c>
-      <c r="BM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>class_label</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>registry-compatible task=text_classification training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>text-classification</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="inlineStr"/>
       <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>text-classification</t>
+        </is>
+      </c>
       <c r="CC2" t="inlineStr"/>
       <c r="CD2" t="inlineStr"/>
       <c r="CE2" t="inlineStr"/>
@@ -1131,7 +1166,12 @@
       <c r="CI2" t="inlineStr"/>
       <c r="CJ2" t="inlineStr"/>
       <c r="CK2" t="inlineStr"/>
-      <c r="CL2" t="inlineStr">
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "rotten_tomatoes", "dataset_variant": 0, "knob_variant": 0, "model_family": "tinybert", "model_registry_key": "tinybert-general-4l_textcls", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -1239,7 +1279,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "learning_rate": 2e-05, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 2e-05, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1330,58 +1370,68 @@
       <c r="BJ3" t="b">
         <v>1</v>
       </c>
-      <c r="BK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL3" t="n">
+      <c r="BK3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN3" t="n">
         <v>4</v>
       </c>
-      <c r="BM3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>class_label</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>registry-compatible task=text_classification training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>text-classification</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="inlineStr"/>
       <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>text-classification</t>
+        </is>
+      </c>
       <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr"/>
       <c r="CE3" t="inlineStr"/>
@@ -1391,7 +1441,12 @@
       <c r="CI3" t="inlineStr"/>
       <c r="CJ3" t="inlineStr"/>
       <c r="CK3" t="inlineStr"/>
-      <c r="CL3" t="inlineStr">
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "glue_cola", "dataset_variant": 0, "knob_variant": 0, "model_family": "albert", "model_registry_key": "albert-base-v2_textcls", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -1499,7 +1554,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 0.0001, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.0001, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1590,58 +1645,68 @@
       <c r="BJ4" t="b">
         <v>1</v>
       </c>
-      <c r="BK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL4" t="n">
+      <c r="BK4" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN4" t="n">
         <v>4</v>
       </c>
-      <c r="BM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS4" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>token_label</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>registry-compatible task=token_classification training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>token-classification</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="inlineStr"/>
       <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>token-classification</t>
+        </is>
+      </c>
       <c r="CC4" t="inlineStr"/>
       <c r="CD4" t="inlineStr"/>
       <c r="CE4" t="inlineStr"/>
@@ -1651,7 +1716,12 @@
       <c r="CI4" t="inlineStr"/>
       <c r="CJ4" t="inlineStr"/>
       <c r="CK4" t="inlineStr"/>
-      <c r="CL4" t="inlineStr">
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "conllpp", "dataset_variant": 0, "knob_variant": 0, "model_family": "roberta", "model_registry_key": "roberta-base_tokencls", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -1759,7 +1829,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "learning_rate": 0.0001, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.0001, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1850,58 +1920,68 @@
       <c r="BJ5" t="b">
         <v>1</v>
       </c>
-      <c r="BK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL5" t="n">
+      <c r="BK5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN5" t="n">
         <v>4</v>
       </c>
-      <c r="BM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS5" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>token_label</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>registry-compatible task=token_classification training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>token-classification</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>token-classification</t>
+        </is>
+      </c>
       <c r="CC5" t="inlineStr"/>
       <c r="CD5" t="inlineStr"/>
       <c r="CE5" t="inlineStr"/>
@@ -1911,7 +1991,12 @@
       <c r="CI5" t="inlineStr"/>
       <c r="CJ5" t="inlineStr"/>
       <c r="CK5" t="inlineStr"/>
-      <c r="CL5" t="inlineStr">
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "conllpp", "dataset_variant": 0, "knob_variant": 0, "model_family": "mobilebert", "model_registry_key": "mobilebert-uncased_tokencls", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -2019,7 +2104,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 2e-05, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 2e-05, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2110,58 +2195,68 @@
       <c r="BJ6" t="b">
         <v>1</v>
       </c>
-      <c r="BK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL6" t="n">
+      <c r="BK6" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL6" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN6" t="n">
         <v>4</v>
       </c>
-      <c r="BM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS6" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>similarity_score</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>registry-compatible task=sentence_similarity training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>sentence-similarity</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>sentence-similarity</t>
+        </is>
+      </c>
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
       <c r="CE6" t="inlineStr"/>
@@ -2171,7 +2266,12 @@
       <c r="CI6" t="inlineStr"/>
       <c r="CJ6" t="inlineStr"/>
       <c r="CK6" t="inlineStr"/>
-      <c r="CL6" t="inlineStr">
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "glue_stsb", "dataset_variant": 0, "knob_variant": 0, "model_family": "tinybert", "model_registry_key": "tinybert-general-4l_similarity", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -2279,7 +2379,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "learning_rate": 5e-05, "max_length": 192, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 5e-05, "max_length": 192, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2370,58 +2470,68 @@
       <c r="BJ7" t="b">
         <v>1</v>
       </c>
-      <c r="BK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL7" t="n">
+      <c r="BK7" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN7" t="n">
         <v>4</v>
       </c>
-      <c r="BM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS7" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>similarity_score</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>registry-compatible task=sentence_similarity training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>sentence-similarity</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="inlineStr"/>
       <c r="CA7" t="inlineStr"/>
-      <c r="CB7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>sentence-similarity</t>
+        </is>
+      </c>
       <c r="CC7" t="inlineStr"/>
       <c r="CD7" t="inlineStr"/>
       <c r="CE7" t="inlineStr"/>
@@ -2431,7 +2541,12 @@
       <c r="CI7" t="inlineStr"/>
       <c r="CJ7" t="inlineStr"/>
       <c r="CK7" t="inlineStr"/>
-      <c r="CL7" t="inlineStr">
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "glue_rte_similarity", "dataset_variant": 0, "knob_variant": 0, "model_family": "bert", "model_registry_key": "bert-base-uncased_similarity", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -2535,7 +2650,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 0.0001, "max_length": 192, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.0001, "max_length": 192, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2626,58 +2741,68 @@
       <c r="BJ8" t="b">
         <v>1</v>
       </c>
-      <c r="BK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL8" t="n">
+      <c r="BK8" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN8" t="n">
         <v>4</v>
       </c>
-      <c r="BM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS8" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>masked_token</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>registry-compatible task=fill_mask training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>fill-mask</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="inlineStr"/>
       <c r="CA8" t="inlineStr"/>
-      <c r="CB8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>fill-mask</t>
+        </is>
+      </c>
       <c r="CC8" t="inlineStr"/>
       <c r="CD8" t="inlineStr"/>
       <c r="CE8" t="inlineStr"/>
@@ -2687,7 +2812,12 @@
       <c r="CI8" t="inlineStr"/>
       <c r="CJ8" t="inlineStr"/>
       <c r="CK8" t="inlineStr"/>
-      <c r="CL8" t="inlineStr">
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="inlineStr"/>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "tinystories_fillmask", "dataset_variant": 0, "knob_variant": 0, "model_family": "roberta", "model_registry_key": "distilroberta-base_fillmask", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -2795,7 +2925,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 0.0001, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.0001, "max_length": 128, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2886,58 +3016,68 @@
       <c r="BJ9" t="b">
         <v>1</v>
       </c>
-      <c r="BK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL9" t="n">
+      <c r="BK9" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL9" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN9" t="n">
         <v>4</v>
       </c>
-      <c r="BM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS9" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>masked_token</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>registry-compatible task=fill_mask training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>fill-mask</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="inlineStr"/>
       <c r="CA9" t="inlineStr"/>
-      <c r="CB9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>fill-mask</t>
+        </is>
+      </c>
       <c r="CC9" t="inlineStr"/>
       <c r="CD9" t="inlineStr"/>
       <c r="CE9" t="inlineStr"/>
@@ -2947,7 +3087,12 @@
       <c r="CI9" t="inlineStr"/>
       <c r="CJ9" t="inlineStr"/>
       <c r="CK9" t="inlineStr"/>
-      <c r="CL9" t="inlineStr">
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "wikitext2", "dataset_variant": 0, "knob_variant": 0, "model_family": "electra", "model_registry_key": "electra-base-generator_fillmask", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -3055,7 +3200,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "learning_rate": 0.0001, "max_length": 192, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.0001, "max_length": 192, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3146,58 +3291,68 @@
       <c r="BJ10" t="b">
         <v>1</v>
       </c>
-      <c r="BK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL10" t="n">
+      <c r="BK10" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL10" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN10" t="n">
         <v>4</v>
       </c>
-      <c r="BM10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS10" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>generated_token</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>registry-compatible task=text_generation training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>text-generation</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr"/>
       <c r="BY10" t="inlineStr"/>
       <c r="BZ10" t="inlineStr"/>
       <c r="CA10" t="inlineStr"/>
-      <c r="CB10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>text-generation</t>
+        </is>
+      </c>
       <c r="CC10" t="inlineStr"/>
       <c r="CD10" t="inlineStr"/>
       <c r="CE10" t="inlineStr"/>
@@ -3207,7 +3362,12 @@
       <c r="CI10" t="inlineStr"/>
       <c r="CJ10" t="inlineStr"/>
       <c r="CK10" t="inlineStr"/>
-      <c r="CL10" t="inlineStr">
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "rotten_tomatoes_lm", "dataset_variant": 0, "knob_variant": 0, "model_family": "dialogpt", "model_registry_key": "dialogpt-small_textgen", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -3319,7 +3479,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 2e-05, "max_length": 256, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 2e-05, "max_length": 256, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3410,58 +3570,68 @@
       <c r="BJ11" t="b">
         <v>1</v>
       </c>
-      <c r="BK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL11" t="n">
+      <c r="BK11" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL11" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN11" t="n">
         <v>4</v>
       </c>
-      <c r="BM11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS11" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>generated_token</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>registry-compatible task=text_generation training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="inlineStr"/>
-      <c r="BV11" t="inlineStr"/>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>text-generation</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr"/>
       <c r="BY11" t="inlineStr"/>
       <c r="BZ11" t="inlineStr"/>
       <c r="CA11" t="inlineStr"/>
-      <c r="CB11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>text-generation</t>
+        </is>
+      </c>
       <c r="CC11" t="inlineStr"/>
       <c r="CD11" t="inlineStr"/>
       <c r="CE11" t="inlineStr"/>
@@ -3471,7 +3641,12 @@
       <c r="CI11" t="inlineStr"/>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="inlineStr"/>
-      <c r="CL11" t="inlineStr">
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "arxiv_summarization_lm", "dataset_variant": 0, "knob_variant": 0, "model_family": "opt", "model_registry_key": "opt-125m_textgen", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -3583,7 +3758,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "learning_rate": 0.0001, "max_length": 256, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.0001, "max_length": 256, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3674,58 +3849,68 @@
       <c r="BJ12" t="b">
         <v>1</v>
       </c>
-      <c r="BK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL12" t="n">
+      <c r="BK12" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL12" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN12" t="n">
         <v>4</v>
       </c>
-      <c r="BM12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS12" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>summary_token</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>registry-compatible task=text2text_generation training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr"/>
-      <c r="BU12" t="inlineStr"/>
-      <c r="BV12" t="inlineStr"/>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>text2text-generation</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="inlineStr"/>
       <c r="CA12" t="inlineStr"/>
-      <c r="CB12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>text2text-generation</t>
+        </is>
+      </c>
       <c r="CC12" t="inlineStr"/>
       <c r="CD12" t="inlineStr"/>
       <c r="CE12" t="inlineStr"/>
@@ -3735,7 +3920,12 @@
       <c r="CI12" t="inlineStr"/>
       <c r="CJ12" t="inlineStr"/>
       <c r="CK12" t="inlineStr"/>
-      <c r="CL12" t="inlineStr">
+      <c r="CL12" t="inlineStr"/>
+      <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "cnn_dailymail", "dataset_variant": 0, "knob_variant": 0, "model_family": "t5", "model_registry_key": "flan-t5-base_text2text", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -3847,7 +4037,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 2e-05, "max_length": 256, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 2e-05, "max_length": 256, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3938,58 +4128,68 @@
       <c r="BJ13" t="b">
         <v>1</v>
       </c>
-      <c r="BK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL13" t="n">
+      <c r="BK13" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL13" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN13" t="n">
         <v>4</v>
       </c>
-      <c r="BM13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS13" t="inlineStr">
         <is>
           <t>integrated_gradients</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BT13" t="inlineStr">
         <is>
           <t>summary_token</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BU13" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="BV13" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BW13" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
+      <c r="BX13" t="inlineStr">
         <is>
           <t>registry-compatible task=text2text_generation training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT13" t="inlineStr"/>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="inlineStr"/>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>text2text-generation</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="inlineStr"/>
       <c r="CA13" t="inlineStr"/>
-      <c r="CB13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>text2text-generation</t>
+        </is>
+      </c>
       <c r="CC13" t="inlineStr"/>
       <c r="CD13" t="inlineStr"/>
       <c r="CE13" t="inlineStr"/>
@@ -3999,7 +4199,12 @@
       <c r="CI13" t="inlineStr"/>
       <c r="CJ13" t="inlineStr"/>
       <c r="CK13" t="inlineStr"/>
-      <c r="CL13" t="inlineStr">
+      <c r="CL13" t="inlineStr"/>
+      <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "cnn_dailymail", "dataset_variant": 0, "knob_variant": 0, "model_family": "codet5", "model_registry_key": "codet5-small_text2text", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -4107,7 +4312,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "learning_rate": 2e-05, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 2e-05, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4196,50 +4401,60 @@
       <c r="BJ14" t="b">
         <v>1</v>
       </c>
-      <c r="BK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL14" t="n">
+      <c r="BK14" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL14" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN14" t="n">
         <v>4</v>
       </c>
-      <c r="BM14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN14" t="inlineStr"/>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr">
+      <c r="BO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ14" t="inlineStr">
+      <c r="BV14" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR14" t="inlineStr">
+      <c r="BW14" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS14" t="inlineStr">
+      <c r="BX14" t="inlineStr">
         <is>
           <t>registry-compatible task=image_classification training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>image-classification</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="inlineStr"/>
       <c r="CA14" t="inlineStr"/>
-      <c r="CB14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>image-classification</t>
+        </is>
+      </c>
       <c r="CC14" t="inlineStr"/>
       <c r="CD14" t="inlineStr"/>
       <c r="CE14" t="inlineStr"/>
@@ -4249,7 +4464,12 @@
       <c r="CI14" t="inlineStr"/>
       <c r="CJ14" t="inlineStr"/>
       <c r="CK14" t="inlineStr"/>
-      <c r="CL14" t="inlineStr">
+      <c r="CL14" t="inlineStr"/>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "fashion_mnist", "dataset_variant": 0, "knob_variant": 0, "model_family": "deit", "model_registry_key": "deit-tiny-patch16-224_imgcls", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -4357,7 +4577,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "learning_rate": 5e-05, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 5e-05, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4446,50 +4666,60 @@
       <c r="BJ15" t="b">
         <v>1</v>
       </c>
-      <c r="BK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL15" t="n">
+      <c r="BK15" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL15" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN15" t="n">
         <v>4</v>
       </c>
-      <c r="BM15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN15" t="inlineStr"/>
-      <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr">
+      <c r="BO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ15" t="inlineStr">
+      <c r="BV15" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR15" t="inlineStr">
+      <c r="BW15" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS15" t="inlineStr">
+      <c r="BX15" t="inlineStr">
         <is>
           <t>registry-compatible task=image_classification training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT15" t="inlineStr"/>
-      <c r="BU15" t="inlineStr"/>
-      <c r="BV15" t="inlineStr"/>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>image-classification</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr"/>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="inlineStr"/>
       <c r="CA15" t="inlineStr"/>
-      <c r="CB15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>image-classification</t>
+        </is>
+      </c>
       <c r="CC15" t="inlineStr"/>
       <c r="CD15" t="inlineStr"/>
       <c r="CE15" t="inlineStr"/>
@@ -4499,7 +4729,12 @@
       <c r="CI15" t="inlineStr"/>
       <c r="CJ15" t="inlineStr"/>
       <c r="CK15" t="inlineStr"/>
-      <c r="CL15" t="inlineStr">
+      <c r="CL15" t="inlineStr"/>
+      <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "fashion_mnist", "dataset_variant": 0, "knob_variant": 0, "model_family": "resnet", "model_registry_key": "resnet-50_imgcls", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -4607,7 +4842,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 2e-05, "max_samples": 96, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 2e-05, "max_samples": 96, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4696,50 +4931,60 @@
       <c r="BJ16" t="b">
         <v>1</v>
       </c>
-      <c r="BK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL16" t="n">
+      <c r="BK16" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL16" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN16" t="n">
         <v>4</v>
       </c>
-      <c r="BM16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN16" t="inlineStr"/>
-      <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr">
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ16" t="inlineStr">
+      <c r="BV16" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR16" t="inlineStr">
+      <c r="BW16" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS16" t="inlineStr">
+      <c r="BX16" t="inlineStr">
         <is>
           <t>registry-compatible task=object_detection training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT16" t="inlineStr"/>
-      <c r="BU16" t="inlineStr"/>
-      <c r="BV16" t="inlineStr"/>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>object-detection</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="inlineStr"/>
       <c r="CA16" t="inlineStr"/>
-      <c r="CB16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>object-detection</t>
+        </is>
+      </c>
       <c r="CC16" t="inlineStr"/>
       <c r="CD16" t="inlineStr"/>
       <c r="CE16" t="inlineStr"/>
@@ -4749,7 +4994,12 @@
       <c r="CI16" t="inlineStr"/>
       <c r="CJ16" t="inlineStr"/>
       <c r="CK16" t="inlineStr"/>
-      <c r="CL16" t="inlineStr">
+      <c r="CL16" t="inlineStr"/>
+      <c r="CM16" t="inlineStr"/>
+      <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="inlineStr"/>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "german_traffic_sign_detection", "dataset_variant": 0, "knob_variant": 0, "model_family": "yolos", "model_registry_key": "yolos-small_objdet", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -4853,7 +5103,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 2e-05, "max_samples": 96, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 2e-05, "max_samples": 96, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4946,50 +5196,60 @@
       <c r="BJ17" t="b">
         <v>1</v>
       </c>
-      <c r="BK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL17" t="n">
+      <c r="BK17" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL17" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN17" t="n">
         <v>4</v>
       </c>
-      <c r="BM17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN17" t="inlineStr"/>
-      <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr">
+      <c r="BO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ17" t="inlineStr">
+      <c r="BV17" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR17" t="inlineStr">
+      <c r="BW17" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS17" t="inlineStr">
+      <c r="BX17" t="inlineStr">
         <is>
           <t>registry-compatible task=image_segmentation training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT17" t="inlineStr"/>
-      <c r="BU17" t="inlineStr"/>
-      <c r="BV17" t="inlineStr"/>
-      <c r="BW17" t="inlineStr">
-        <is>
-          <t>image-segmentation</t>
-        </is>
-      </c>
-      <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="inlineStr"/>
       <c r="CA17" t="inlineStr"/>
-      <c r="CB17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>image-segmentation</t>
+        </is>
+      </c>
       <c r="CC17" t="inlineStr"/>
       <c r="CD17" t="inlineStr"/>
       <c r="CE17" t="inlineStr"/>
@@ -4999,7 +5259,12 @@
       <c r="CI17" t="inlineStr"/>
       <c r="CJ17" t="inlineStr"/>
       <c r="CK17" t="inlineStr"/>
-      <c r="CL17" t="inlineStr">
+      <c r="CL17" t="inlineStr"/>
+      <c r="CM17" t="inlineStr"/>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "ade20k_mini_segmentation", "dataset_variant": 0, "knob_variant": 0, "model_family": "segformer", "model_registry_key": "segformer-b1_seg", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -5103,7 +5368,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "learning_rate": 2e-05, "max_samples": 96, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 2e-05, "max_samples": 96, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5196,50 +5461,60 @@
       <c r="BJ18" t="b">
         <v>1</v>
       </c>
-      <c r="BK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL18" t="n">
+      <c r="BK18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN18" t="n">
         <v>4</v>
       </c>
-      <c r="BM18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN18" t="inlineStr"/>
-      <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr">
+      <c r="BO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ18" t="inlineStr">
+      <c r="BV18" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR18" t="inlineStr">
+      <c r="BW18" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS18" t="inlineStr">
+      <c r="BX18" t="inlineStr">
         <is>
           <t>registry-compatible task=image_segmentation training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT18" t="inlineStr"/>
-      <c r="BU18" t="inlineStr"/>
-      <c r="BV18" t="inlineStr"/>
-      <c r="BW18" t="inlineStr">
-        <is>
-          <t>image-segmentation</t>
-        </is>
-      </c>
-      <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="inlineStr"/>
       <c r="CA18" t="inlineStr"/>
-      <c r="CB18" t="inlineStr"/>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>image-segmentation</t>
+        </is>
+      </c>
       <c r="CC18" t="inlineStr"/>
       <c r="CD18" t="inlineStr"/>
       <c r="CE18" t="inlineStr"/>
@@ -5249,7 +5524,12 @@
       <c r="CI18" t="inlineStr"/>
       <c r="CJ18" t="inlineStr"/>
       <c r="CK18" t="inlineStr"/>
-      <c r="CL18" t="inlineStr">
+      <c r="CL18" t="inlineStr"/>
+      <c r="CM18" t="inlineStr"/>
+      <c r="CN18" t="inlineStr"/>
+      <c r="CO18" t="inlineStr"/>
+      <c r="CP18" t="inlineStr"/>
+      <c r="CQ18" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "hot_building_segmentation", "dataset_variant": 0, "knob_variant": 0, "model_family": "segformer", "model_registry_key": "segformer-b4_seg", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -5357,7 +5637,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "learning_rate": 0.0001, "max_length": 64, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 8, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.0001, "max_length": 64, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 2, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5452,50 +5732,60 @@
       <c r="BJ19" t="b">
         <v>1</v>
       </c>
-      <c r="BK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL19" t="n">
+      <c r="BK19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL19" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN19" t="n">
         <v>4</v>
       </c>
-      <c r="BM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN19" t="inlineStr"/>
-      <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr">
+      <c r="BO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ19" t="inlineStr">
+      <c r="BV19" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR19" t="inlineStr">
+      <c r="BW19" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS19" t="inlineStr">
+      <c r="BX19" t="inlineStr">
         <is>
           <t>registry-compatible task=image_captioning training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT19" t="inlineStr"/>
-      <c r="BU19" t="inlineStr"/>
-      <c r="BV19" t="inlineStr"/>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>image-to-text</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="inlineStr"/>
       <c r="CA19" t="inlineStr"/>
-      <c r="CB19" t="inlineStr"/>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>image-to-text</t>
+        </is>
+      </c>
       <c r="CC19" t="inlineStr"/>
       <c r="CD19" t="inlineStr"/>
       <c r="CE19" t="inlineStr"/>
@@ -5505,7 +5795,12 @@
       <c r="CI19" t="inlineStr"/>
       <c r="CJ19" t="inlineStr"/>
       <c r="CK19" t="inlineStr"/>
-      <c r="CL19" t="inlineStr">
+      <c r="CL19" t="inlineStr"/>
+      <c r="CM19" t="inlineStr"/>
+      <c r="CN19" t="inlineStr"/>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="inlineStr"/>
+      <c r="CQ19" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "flickr8k_captioning", "dataset_variant": 0, "knob_variant": 0, "model_family": "git", "model_registry_key": "git-base-coco-caption", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -5613,7 +5908,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "learning_rate": 0.0001, "max_length": 48, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 16, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.0001, "max_length": 48, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5716,50 +6011,60 @@
       <c r="BJ20" t="b">
         <v>1</v>
       </c>
-      <c r="BK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL20" t="n">
+      <c r="BK20" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL20" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN20" t="n">
         <v>4</v>
       </c>
-      <c r="BM20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN20" t="inlineStr"/>
-      <c r="BO20" t="inlineStr"/>
-      <c r="BP20" t="inlineStr">
+      <c r="BO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr">
         <is>
           <t>hf_registry</t>
         </is>
       </c>
-      <c r="BQ20" t="inlineStr">
+      <c r="BV20" t="inlineStr">
         <is>
           <t>task_head</t>
         </is>
       </c>
-      <c r="BR20" t="inlineStr">
+      <c r="BW20" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS20" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>registry-compatible task=visual_question_answering training_regime=finetune_transfer</t>
         </is>
       </c>
-      <c r="BT20" t="inlineStr"/>
-      <c r="BU20" t="inlineStr"/>
-      <c r="BV20" t="inlineStr"/>
-      <c r="BW20" t="inlineStr">
-        <is>
-          <t>visual-question-answering</t>
-        </is>
-      </c>
-      <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="inlineStr"/>
       <c r="CA20" t="inlineStr"/>
-      <c r="CB20" t="inlineStr"/>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>visual-question-answering</t>
+        </is>
+      </c>
       <c r="CC20" t="inlineStr"/>
       <c r="CD20" t="inlineStr"/>
       <c r="CE20" t="inlineStr"/>
@@ -5769,7 +6074,12 @@
       <c r="CI20" t="inlineStr"/>
       <c r="CJ20" t="inlineStr"/>
       <c r="CK20" t="inlineStr"/>
-      <c r="CL20" t="inlineStr">
+      <c r="CL20" t="inlineStr"/>
+      <c r="CM20" t="inlineStr"/>
+      <c r="CN20" t="inlineStr"/>
+      <c r="CO20" t="inlineStr"/>
+      <c r="CP20" t="inlineStr"/>
+      <c r="CQ20" t="inlineStr">
         <is>
           <t>{"dataset_registry_key": "vqav2", "dataset_variant": 0, "knob_variant": 0, "model_family": "blip", "model_registry_key": "blip-vqa-base", "split_variant": 0, "training_regime": "finetune_transfer"}</t>
         </is>
@@ -5853,7 +6163,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -5934,42 +6244,52 @@
       <c r="BJ21" t="b">
         <v>1</v>
       </c>
-      <c r="BK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL21" t="n">
+      <c r="BK21" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL21" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN21" t="n">
         <v>4</v>
       </c>
-      <c r="BM21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN21" t="inlineStr"/>
-      <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr">
+      <c r="BO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS21" t="inlineStr"/>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr">
         <is>
           <t>generic_registry</t>
         </is>
       </c>
-      <c r="BQ21" t="inlineStr">
+      <c r="BV21" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="BR21" t="inlineStr">
+      <c r="BW21" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS21" t="inlineStr">
+      <c r="BX21" t="inlineStr">
         <is>
           <t>generic manifest-compatible task runner</t>
         </is>
       </c>
-      <c r="BT21" t="inlineStr"/>
-      <c r="BU21" t="inlineStr"/>
-      <c r="BV21" t="inlineStr"/>
-      <c r="BW21" t="inlineStr"/>
-      <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="inlineStr"/>
       <c r="CA21" t="inlineStr"/>
@@ -5984,6 +6304,11 @@
       <c r="CJ21" t="inlineStr"/>
       <c r="CK21" t="inlineStr"/>
       <c r="CL21" t="inlineStr"/>
+      <c r="CM21" t="inlineStr"/>
+      <c r="CN21" t="inlineStr"/>
+      <c r="CO21" t="inlineStr"/>
+      <c r="CP21" t="inlineStr"/>
+      <c r="CQ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6063,7 +6388,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>{"batch_size": 64, "device": "auto", "distribution_type": "iid", "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "none", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 64, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "none", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6144,42 +6469,52 @@
       <c r="BJ22" t="b">
         <v>1</v>
       </c>
-      <c r="BK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL22" t="n">
+      <c r="BK22" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL22" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN22" t="n">
         <v>4</v>
       </c>
-      <c r="BM22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN22" t="inlineStr"/>
-      <c r="BO22" t="inlineStr"/>
-      <c r="BP22" t="inlineStr">
+      <c r="BO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+      <c r="BU22" t="inlineStr">
         <is>
           <t>generic_registry</t>
         </is>
       </c>
-      <c r="BQ22" t="inlineStr">
+      <c r="BV22" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="BR22" t="inlineStr">
+      <c r="BW22" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS22" t="inlineStr">
+      <c r="BX22" t="inlineStr">
         <is>
           <t>generic manifest-compatible task runner</t>
         </is>
       </c>
-      <c r="BT22" t="inlineStr"/>
-      <c r="BU22" t="inlineStr"/>
-      <c r="BV22" t="inlineStr"/>
-      <c r="BW22" t="inlineStr"/>
-      <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="inlineStr"/>
       <c r="CA22" t="inlineStr"/>
@@ -6194,6 +6529,11 @@
       <c r="CJ22" t="inlineStr"/>
       <c r="CK22" t="inlineStr"/>
       <c r="CL22" t="inlineStr"/>
+      <c r="CM22" t="inlineStr"/>
+      <c r="CN22" t="inlineStr"/>
+      <c r="CO22" t="inlineStr"/>
+      <c r="CP22" t="inlineStr"/>
+      <c r="CQ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6273,7 +6613,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "adam", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6354,42 +6694,52 @@
       <c r="BJ23" t="b">
         <v>1</v>
       </c>
-      <c r="BK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL23" t="n">
+      <c r="BK23" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL23" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN23" t="n">
         <v>4</v>
       </c>
-      <c r="BM23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN23" t="inlineStr"/>
-      <c r="BO23" t="inlineStr"/>
-      <c r="BP23" t="inlineStr">
+      <c r="BO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr"/>
+      <c r="BU23" t="inlineStr">
         <is>
           <t>generic_registry</t>
         </is>
       </c>
-      <c r="BQ23" t="inlineStr">
+      <c r="BV23" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="BR23" t="inlineStr">
+      <c r="BW23" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS23" t="inlineStr">
+      <c r="BX23" t="inlineStr">
         <is>
           <t>generic manifest-compatible task runner</t>
         </is>
       </c>
-      <c r="BT23" t="inlineStr"/>
-      <c r="BU23" t="inlineStr"/>
-      <c r="BV23" t="inlineStr"/>
-      <c r="BW23" t="inlineStr"/>
-      <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="inlineStr"/>
       <c r="CA23" t="inlineStr"/>
@@ -6404,6 +6754,11 @@
       <c r="CJ23" t="inlineStr"/>
       <c r="CK23" t="inlineStr"/>
       <c r="CL23" t="inlineStr"/>
+      <c r="CM23" t="inlineStr"/>
+      <c r="CN23" t="inlineStr"/>
+      <c r="CO23" t="inlineStr"/>
+      <c r="CP23" t="inlineStr"/>
+      <c r="CQ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6483,7 +6838,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "none", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 32, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "none", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 3, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -6564,42 +6919,52 @@
       <c r="BJ24" t="b">
         <v>1</v>
       </c>
-      <c r="BK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL24" t="n">
+      <c r="BK24" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL24" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN24" t="n">
         <v>4</v>
       </c>
-      <c r="BM24" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN24" t="inlineStr"/>
-      <c r="BO24" t="inlineStr"/>
-      <c r="BP24" t="inlineStr">
+      <c r="BO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+      <c r="BU24" t="inlineStr">
         <is>
           <t>generic_registry</t>
         </is>
       </c>
-      <c r="BQ24" t="inlineStr">
+      <c r="BV24" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="BR24" t="inlineStr">
+      <c r="BW24" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS24" t="inlineStr">
+      <c r="BX24" t="inlineStr">
         <is>
           <t>generic manifest-compatible task runner</t>
         </is>
       </c>
-      <c r="BT24" t="inlineStr"/>
-      <c r="BU24" t="inlineStr"/>
-      <c r="BV24" t="inlineStr"/>
-      <c r="BW24" t="inlineStr"/>
-      <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="inlineStr"/>
       <c r="CA24" t="inlineStr"/>
@@ -6614,6 +6979,11 @@
       <c r="CJ24" t="inlineStr"/>
       <c r="CK24" t="inlineStr"/>
       <c r="CL24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr"/>
+      <c r="CN24" t="inlineStr"/>
+      <c r="CO24" t="inlineStr"/>
+      <c r="CP24" t="inlineStr"/>
+      <c r="CQ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6693,7 +7063,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>{"batch_size": 64, "device": "auto", "distribution_type": "iid", "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "none", "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
+          <t>{"batch_size": 64, "device": "auto", "distribution_type": "iid", "enable_perturbation_metrics": true, "learning_rate": 0.001, "max_samples": 128, "mixed_precision": false, "momentum": 0.0, "optimizer": "none", "perturbation_sample_count": 1, "save_weights": false, "split_strategy": "iid", "timeout_s": 3600, "training_epochs": 1, "weight_decay": 0.0}</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -6774,42 +7144,52 @@
       <c r="BJ25" t="b">
         <v>1</v>
       </c>
-      <c r="BK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL25" t="n">
+      <c r="BK25" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL25" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN25" t="n">
         <v>4</v>
       </c>
-      <c r="BM25" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN25" t="inlineStr"/>
-      <c r="BO25" t="inlineStr"/>
-      <c r="BP25" t="inlineStr">
+      <c r="BO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr">
         <is>
           <t>generic_registry</t>
         </is>
       </c>
-      <c r="BQ25" t="inlineStr">
+      <c r="BV25" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="BR25" t="inlineStr">
+      <c r="BW25" t="inlineStr">
         <is>
           <t>compatible</t>
         </is>
       </c>
-      <c r="BS25" t="inlineStr">
+      <c r="BX25" t="inlineStr">
         <is>
           <t>generic manifest-compatible task runner</t>
         </is>
       </c>
-      <c r="BT25" t="inlineStr"/>
-      <c r="BU25" t="inlineStr"/>
-      <c r="BV25" t="inlineStr"/>
-      <c r="BW25" t="inlineStr"/>
-      <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="inlineStr"/>
       <c r="CA25" t="inlineStr"/>
@@ -6824,6 +7204,11 @@
       <c r="CJ25" t="inlineStr"/>
       <c r="CK25" t="inlineStr"/>
       <c r="CL25" t="inlineStr"/>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
+      <c r="CP25" t="inlineStr"/>
+      <c r="CQ25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
